--- a/TablasAnalisis/Cobertura_de_salud_porcentaje.xlsx
+++ b/TablasAnalisis/Cobertura_de_salud_porcentaje.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F505"/>
+  <dimension ref="A1:H505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,16 @@
           <t>porcentaje_sin_cobertura_en_2022</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>diferencia_porcentaje_con_cobertura</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>diferencia_porcentaje_sin_cobertura</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -471,6 +481,12 @@
       <c r="F2" t="n">
         <v>46.12</v>
       </c>
+      <c r="G2" t="n">
+        <v>-2.489999999999995</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.489999999999995</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -495,6 +511,12 @@
       <c r="F3" t="n">
         <v>42.76</v>
       </c>
+      <c r="G3" t="n">
+        <v>-1.640000000000001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.640000000000001</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -519,6 +541,12 @@
       <c r="F4" t="n">
         <v>40.81</v>
       </c>
+      <c r="G4" t="n">
+        <v>1.689999999999998</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-1.689999999999998</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -543,6 +571,12 @@
       <c r="F5" t="n">
         <v>40.93</v>
       </c>
+      <c r="G5" t="n">
+        <v>4.560000000000002</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-4.560000000000002</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -567,6 +601,12 @@
       <c r="F6" t="n">
         <v>52.12</v>
       </c>
+      <c r="G6" t="n">
+        <v>-3.589999999999996</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.589999999999996</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -591,6 +631,12 @@
       <c r="F7" t="n">
         <v>49.9</v>
       </c>
+      <c r="G7" t="n">
+        <v>-8.689999999999998</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8.689999999999998</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -615,6 +661,12 @@
       <c r="F8" t="n">
         <v>41.56</v>
       </c>
+      <c r="G8" t="n">
+        <v>-5.620000000000005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5.620000000000005</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -639,6 +691,12 @@
       <c r="F9" t="n">
         <v>36.09</v>
       </c>
+      <c r="G9" t="n">
+        <v>-1.920000000000002</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.920000000000002</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -663,6 +721,12 @@
       <c r="F10" t="n">
         <v>33.27</v>
       </c>
+      <c r="G10" t="n">
+        <v>0.7600000000000051</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.759999999999998</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -687,6 +751,12 @@
       <c r="F11" t="n">
         <v>32.03</v>
       </c>
+      <c r="G11" t="n">
+        <v>1.870000000000005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-1.869999999999997</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -711,6 +781,12 @@
       <c r="F12" t="n">
         <v>31.39</v>
       </c>
+      <c r="G12" t="n">
+        <v>3.019999999999996</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-3.019999999999996</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -735,6 +811,12 @@
       <c r="F13" t="n">
         <v>30.46</v>
       </c>
+      <c r="G13" t="n">
+        <v>2.720000000000013</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-2.719999999999999</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -759,6 +841,12 @@
       <c r="F14" t="n">
         <v>21.82</v>
       </c>
+      <c r="G14" t="n">
+        <v>1.210000000000008</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-1.210000000000001</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -783,6 +871,12 @@
       <c r="F15" t="n">
         <v>7.36</v>
       </c>
+      <c r="G15" t="n">
+        <v>0.1099999999999994</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.1099999999999994</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -807,6 +901,12 @@
       <c r="F16" t="n">
         <v>2.86</v>
       </c>
+      <c r="G16" t="n">
+        <v>0.7199999999999989</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.7200000000000002</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -831,6 +931,12 @@
       <c r="F17" t="n">
         <v>2.36</v>
       </c>
+      <c r="G17" t="n">
+        <v>0.9399999999999977</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -855,6 +961,12 @@
       <c r="F18" t="n">
         <v>2.25</v>
       </c>
+      <c r="G18" t="n">
+        <v>0.1599999999999966</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.1600000000000001</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -879,6 +991,12 @@
       <c r="F19" t="n">
         <v>2.55</v>
       </c>
+      <c r="G19" t="n">
+        <v>-0.6599999999999966</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.6599999999999999</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -903,6 +1021,12 @@
       <c r="F20" t="n">
         <v>4.65</v>
       </c>
+      <c r="G20" t="n">
+        <v>-2.13000000000001</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.13</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -927,6 +1051,12 @@
       <c r="F21" t="n">
         <v>11.87</v>
       </c>
+      <c r="G21" t="n">
+        <v>-8.359999999999999</v>
+      </c>
+      <c r="H21" t="n">
+        <v>8.359999999999999</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -951,6 +1081,12 @@
       <c r="F22" t="n">
         <v>7.2</v>
       </c>
+      <c r="G22" t="n">
+        <v>4.329999999999998</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-4.329999999999999</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -975,6 +1111,12 @@
       <c r="F23" t="n">
         <v>19.77</v>
       </c>
+      <c r="G23" t="n">
+        <v>5.170000000000002</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-5.170000000000002</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -999,6 +1141,12 @@
       <c r="F24" t="n">
         <v>20.03</v>
       </c>
+      <c r="G24" t="n">
+        <v>2.679999999999993</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-2.68</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1023,6 +1171,12 @@
       <c r="F25" t="n">
         <v>19.91</v>
       </c>
+      <c r="G25" t="n">
+        <v>3.980000000000004</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-3.98</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1047,6 +1201,12 @@
       <c r="F26" t="n">
         <v>20.81</v>
       </c>
+      <c r="G26" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-4.75</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1071,6 +1231,12 @@
       <c r="F27" t="n">
         <v>27.67</v>
       </c>
+      <c r="G27" t="n">
+        <v>0.1099999999999994</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-0.1099999999999994</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1095,6 +1261,12 @@
       <c r="F28" t="n">
         <v>25.94</v>
       </c>
+      <c r="G28" t="n">
+        <v>-1.899999999999991</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.900000000000002</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1119,6 +1291,12 @@
       <c r="F29" t="n">
         <v>20.27</v>
       </c>
+      <c r="G29" t="n">
+        <v>-1.060000000000002</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.059999999999999</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1143,6 +1321,12 @@
       <c r="F30" t="n">
         <v>17.37</v>
       </c>
+      <c r="G30" t="n">
+        <v>0.9899999999999949</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-0.9899999999999984</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1167,6 +1351,12 @@
       <c r="F31" t="n">
         <v>15.95</v>
       </c>
+      <c r="G31" t="n">
+        <v>2.219999999999999</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-2.220000000000002</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1191,6 +1381,12 @@
       <c r="F32" t="n">
         <v>15.45</v>
       </c>
+      <c r="G32" t="n">
+        <v>1.379999999999995</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-1.379999999999999</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1215,6 +1411,12 @@
       <c r="F33" t="n">
         <v>17.29</v>
       </c>
+      <c r="G33" t="n">
+        <v>-0.8800000000000097</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.879999999999999</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1239,6 +1441,12 @@
       <c r="F34" t="n">
         <v>15.23</v>
       </c>
+      <c r="G34" t="n">
+        <v>0.2599999999999909</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-0.2599999999999998</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1263,6 +1471,12 @@
       <c r="F35" t="n">
         <v>11.84</v>
       </c>
+      <c r="G35" t="n">
+        <v>-1.100000000000009</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1287,6 +1501,12 @@
       <c r="F36" t="n">
         <v>5.8</v>
       </c>
+      <c r="G36" t="n">
+        <v>-0.5600000000000023</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.5599999999999996</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1311,6 +1531,12 @@
       <c r="F37" t="n">
         <v>2.79</v>
       </c>
+      <c r="G37" t="n">
+        <v>-0.04000000000000625</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.04000000000000004</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1335,6 +1561,12 @@
       <c r="F38" t="n">
         <v>2.01</v>
       </c>
+      <c r="G38" t="n">
+        <v>-0.1500000000000057</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.1499999999999997</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1359,6 +1591,12 @@
       <c r="F39" t="n">
         <v>1.6</v>
       </c>
+      <c r="G39" t="n">
+        <v>-0.1799999999999926</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.1800000000000002</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1383,6 +1621,12 @@
       <c r="F40" t="n">
         <v>1.61</v>
       </c>
+      <c r="G40" t="n">
+        <v>-0.09999999999999432</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.1000000000000001</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1407,6 +1651,12 @@
       <c r="F41" t="n">
         <v>1.77</v>
       </c>
+      <c r="G41" t="n">
+        <v>-0.5099999999999909</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.51</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1431,6 +1681,12 @@
       <c r="F42" t="n">
         <v>3.29</v>
       </c>
+      <c r="G42" t="n">
+        <v>-0.6000000000000085</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.6000000000000001</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1455,6 +1711,12 @@
       <c r="F43" t="n">
         <v>2.77</v>
       </c>
+      <c r="G43" t="n">
+        <v>-0.1899999999999977</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.1899999999999999</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1479,6 +1741,12 @@
       <c r="F44" t="n">
         <v>53.02</v>
       </c>
+      <c r="G44" t="n">
+        <v>-4.630000000000003</v>
+      </c>
+      <c r="H44" t="n">
+        <v>4.630000000000003</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1503,6 +1771,12 @@
       <c r="F45" t="n">
         <v>46.02</v>
       </c>
+      <c r="G45" t="n">
+        <v>-0.5200000000000031</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.5200000000000031</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1527,6 +1801,12 @@
       <c r="F46" t="n">
         <v>41.48</v>
       </c>
+      <c r="G46" t="n">
+        <v>0.1400000000000006</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-0.1400000000000006</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1551,6 +1831,12 @@
       <c r="F47" t="n">
         <v>41.88</v>
       </c>
+      <c r="G47" t="n">
+        <v>-1.850000000000001</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1.850000000000001</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1575,6 +1861,12 @@
       <c r="F48" t="n">
         <v>68.72</v>
       </c>
+      <c r="G48" t="n">
+        <v>-7.490000000000002</v>
+      </c>
+      <c r="H48" t="n">
+        <v>7.490000000000002</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1599,6 +1891,12 @@
       <c r="F49" t="n">
         <v>64.14</v>
       </c>
+      <c r="G49" t="n">
+        <v>-10.81</v>
+      </c>
+      <c r="H49" t="n">
+        <v>10.81</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1623,6 +1921,12 @@
       <c r="F50" t="n">
         <v>50.37</v>
       </c>
+      <c r="G50" t="n">
+        <v>-7.109999999999999</v>
+      </c>
+      <c r="H50" t="n">
+        <v>7.109999999999999</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1647,6 +1951,12 @@
       <c r="F51" t="n">
         <v>41.08</v>
       </c>
+      <c r="G51" t="n">
+        <v>-4.719999999999999</v>
+      </c>
+      <c r="H51" t="n">
+        <v>4.719999999999999</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1671,6 +1981,12 @@
       <c r="F52" t="n">
         <v>36.12</v>
       </c>
+      <c r="G52" t="n">
+        <v>-3.300000000000004</v>
+      </c>
+      <c r="H52" t="n">
+        <v>3.299999999999997</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1695,6 +2011,12 @@
       <c r="F53" t="n">
         <v>32.91</v>
       </c>
+      <c r="G53" t="n">
+        <v>-6.069999999999993</v>
+      </c>
+      <c r="H53" t="n">
+        <v>6.069999999999997</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1719,6 +2041,12 @@
       <c r="F54" t="n">
         <v>29.68</v>
       </c>
+      <c r="G54" t="n">
+        <v>0.8999999999999915</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-0.8999999999999986</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1743,6 +2071,12 @@
       <c r="F55" t="n">
         <v>26.34</v>
       </c>
+      <c r="G55" t="n">
+        <v>2.709999999999994</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-2.710000000000001</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1767,6 +2101,12 @@
       <c r="F56" t="n">
         <v>19.28</v>
       </c>
+      <c r="G56" t="n">
+        <v>2.289999999999992</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-2.289999999999999</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1791,6 +2131,12 @@
       <c r="F57" t="n">
         <v>7.42</v>
       </c>
+      <c r="G57" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-2.25</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1815,6 +2161,12 @@
       <c r="F58" t="n">
         <v>3.02</v>
       </c>
+      <c r="G58" t="n">
+        <v>3.480000000000004</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-3.48</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1839,6 +2191,12 @@
       <c r="F59" t="n">
         <v>2.51</v>
       </c>
+      <c r="G59" t="n">
+        <v>4.069999999999993</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-4.07</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1863,6 +2221,12 @@
       <c r="F60" t="n">
         <v>2.79</v>
       </c>
+      <c r="G60" t="n">
+        <v>2.379999999999995</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-2.38</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1887,6 +2251,12 @@
       <c r="F61" t="n">
         <v>3.32</v>
       </c>
+      <c r="G61" t="n">
+        <v>1.63000000000001</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-1.63</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1911,6 +2281,12 @@
       <c r="F62" t="n">
         <v>3.23</v>
       </c>
+      <c r="G62" t="n">
+        <v>2.780000000000001</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-2.78</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1935,6 +2311,12 @@
       <c r="F63" t="n">
         <v>5.42</v>
       </c>
+      <c r="G63" t="n">
+        <v>0.07999999999999829</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-0.08000000000000007</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1959,6 +2341,12 @@
       <c r="F64" t="n">
         <v>16.67</v>
       </c>
+      <c r="G64" t="n">
+        <v>-11.41</v>
+      </c>
+      <c r="H64" t="n">
+        <v>11.41</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1983,6 +2371,12 @@
       <c r="F65" t="n">
         <v>66.23</v>
       </c>
+      <c r="G65" t="n">
+        <v>4.010000000000002</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-4.009999999999991</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2007,6 +2401,12 @@
       <c r="F66" t="n">
         <v>61.66</v>
       </c>
+      <c r="G66" t="n">
+        <v>6.470000000000002</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-6.469999999999999</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2031,6 +2431,12 @@
       <c r="F67" t="n">
         <v>59.69</v>
       </c>
+      <c r="G67" t="n">
+        <v>6.580000000000005</v>
+      </c>
+      <c r="H67" t="n">
+        <v>-6.579999999999998</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2055,6 +2461,12 @@
       <c r="F68" t="n">
         <v>62.46</v>
       </c>
+      <c r="G68" t="n">
+        <v>4.159999999999997</v>
+      </c>
+      <c r="H68" t="n">
+        <v>-4.160000000000004</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2079,6 +2491,12 @@
       <c r="F69" t="n">
         <v>71.86</v>
       </c>
+      <c r="G69" t="n">
+        <v>-0.4800000000000004</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.480000000000004</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2103,6 +2521,12 @@
       <c r="F70" t="n">
         <v>68.52</v>
       </c>
+      <c r="G70" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1.72999999999999</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2127,6 +2551,12 @@
       <c r="F71" t="n">
         <v>57.15</v>
       </c>
+      <c r="G71" t="n">
+        <v>2.380000000000003</v>
+      </c>
+      <c r="H71" t="n">
+        <v>-2.380000000000003</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2151,6 +2581,12 @@
       <c r="F72" t="n">
         <v>50.87</v>
       </c>
+      <c r="G72" t="n">
+        <v>4.120000000000005</v>
+      </c>
+      <c r="H72" t="n">
+        <v>-4.120000000000005</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2175,6 +2611,12 @@
       <c r="F73" t="n">
         <v>47.99</v>
       </c>
+      <c r="G73" t="n">
+        <v>3.379999999999995</v>
+      </c>
+      <c r="H73" t="n">
+        <v>-3.379999999999995</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2199,6 +2641,12 @@
       <c r="F74" t="n">
         <v>45.79</v>
       </c>
+      <c r="G74" t="n">
+        <v>2.660000000000004</v>
+      </c>
+      <c r="H74" t="n">
+        <v>-2.660000000000004</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2223,6 +2671,12 @@
       <c r="F75" t="n">
         <v>42.03</v>
       </c>
+      <c r="G75" t="n">
+        <v>6.379999999999995</v>
+      </c>
+      <c r="H75" t="n">
+        <v>-6.379999999999995</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2247,6 +2701,12 @@
       <c r="F76" t="n">
         <v>38.47</v>
       </c>
+      <c r="G76" t="n">
+        <v>6.730000000000004</v>
+      </c>
+      <c r="H76" t="n">
+        <v>-6.730000000000004</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2271,6 +2731,12 @@
       <c r="F77" t="n">
         <v>28.77</v>
       </c>
+      <c r="G77" t="n">
+        <v>5.490000000000009</v>
+      </c>
+      <c r="H77" t="n">
+        <v>-5.489999999999998</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2295,6 +2761,12 @@
       <c r="F78" t="n">
         <v>11.75</v>
       </c>
+      <c r="G78" t="n">
+        <v>2.859999999999999</v>
+      </c>
+      <c r="H78" t="n">
+        <v>-2.859999999999999</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2319,6 +2791,12 @@
       <c r="F79" t="n">
         <v>5.17</v>
       </c>
+      <c r="G79" t="n">
+        <v>4.289999999999992</v>
+      </c>
+      <c r="H79" t="n">
+        <v>-4.290000000000001</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2343,6 +2821,12 @@
       <c r="F80" t="n">
         <v>4.03</v>
       </c>
+      <c r="G80" t="n">
+        <v>5.890000000000001</v>
+      </c>
+      <c r="H80" t="n">
+        <v>-5.89</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2367,6 +2851,12 @@
       <c r="F81" t="n">
         <v>3.54</v>
       </c>
+      <c r="G81" t="n">
+        <v>2.719999999999999</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-2.72</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2391,6 +2881,12 @@
       <c r="F82" t="n">
         <v>4.3</v>
       </c>
+      <c r="G82" t="n">
+        <v>4.189999999999998</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-4.19</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2415,6 +2911,12 @@
       <c r="F83" t="n">
         <v>8.27</v>
       </c>
+      <c r="G83" t="n">
+        <v>-0.8399999999999892</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.8399999999999999</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2439,6 +2941,12 @@
       <c r="F84" t="n">
         <v>23.12</v>
       </c>
+      <c r="G84" t="n">
+        <v>-18.05000000000001</v>
+      </c>
+      <c r="H84" t="n">
+        <v>18.05</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2463,6 +2971,12 @@
       <c r="F85" t="n">
         <v>26.47</v>
       </c>
+      <c r="G85" t="n">
+        <v>-22.39</v>
+      </c>
+      <c r="H85" t="n">
+        <v>22.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2487,6 +3001,12 @@
       <c r="F86" t="n">
         <v>32.33</v>
       </c>
+      <c r="G86" t="n">
+        <v>-3.649999999999991</v>
+      </c>
+      <c r="H86" t="n">
+        <v>3.649999999999999</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2511,6 +3031,12 @@
       <c r="F87" t="n">
         <v>29.03</v>
       </c>
+      <c r="G87" t="n">
+        <v>-2.469999999999999</v>
+      </c>
+      <c r="H87" t="n">
+        <v>2.470000000000002</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2535,6 +3061,12 @@
       <c r="F88" t="n">
         <v>26.98</v>
       </c>
+      <c r="G88" t="n">
+        <v>1.379999999999995</v>
+      </c>
+      <c r="H88" t="n">
+        <v>-1.379999999999999</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2559,6 +3091,12 @@
       <c r="F89" t="n">
         <v>29.21</v>
       </c>
+      <c r="G89" t="n">
+        <v>-0.03999999999999204</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.03999999999999915</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2583,6 +3121,12 @@
       <c r="F90" t="n">
         <v>49.31</v>
       </c>
+      <c r="G90" t="n">
+        <v>-7.700000000000003</v>
+      </c>
+      <c r="H90" t="n">
+        <v>7.700000000000003</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2607,6 +3151,12 @@
       <c r="F91" t="n">
         <v>46.17</v>
       </c>
+      <c r="G91" t="n">
+        <v>-13.38</v>
+      </c>
+      <c r="H91" t="n">
+        <v>13.38</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2631,6 +3181,12 @@
       <c r="F92" t="n">
         <v>33.91</v>
       </c>
+      <c r="G92" t="n">
+        <v>-6.609999999999999</v>
+      </c>
+      <c r="H92" t="n">
+        <v>6.609999999999996</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2655,6 +3211,12 @@
       <c r="F93" t="n">
         <v>27.62</v>
       </c>
+      <c r="G93" t="n">
+        <v>-1.600000000000009</v>
+      </c>
+      <c r="H93" t="n">
+        <v>1.600000000000001</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2679,6 +3241,12 @@
       <c r="F94" t="n">
         <v>24.64</v>
       </c>
+      <c r="G94" t="n">
+        <v>0.1200000000000045</v>
+      </c>
+      <c r="H94" t="n">
+        <v>-0.120000000000001</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2703,6 +3271,12 @@
       <c r="F95" t="n">
         <v>23.51</v>
       </c>
+      <c r="G95" t="n">
+        <v>-2.660000000000011</v>
+      </c>
+      <c r="H95" t="n">
+        <v>2.66</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2727,6 +3301,12 @@
       <c r="F96" t="n">
         <v>22.22</v>
       </c>
+      <c r="G96" t="n">
+        <v>3.730000000000004</v>
+      </c>
+      <c r="H96" t="n">
+        <v>-3.73</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2751,6 +3331,12 @@
       <c r="F97" t="n">
         <v>23.19</v>
       </c>
+      <c r="G97" t="n">
+        <v>2.370000000000005</v>
+      </c>
+      <c r="H97" t="n">
+        <v>-2.369999999999997</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2775,6 +3361,12 @@
       <c r="F98" t="n">
         <v>16.08</v>
       </c>
+      <c r="G98" t="n">
+        <v>4.780000000000001</v>
+      </c>
+      <c r="H98" t="n">
+        <v>-4.780000000000001</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2799,6 +3391,12 @@
       <c r="F99" t="n">
         <v>5.89</v>
       </c>
+      <c r="G99" t="n">
+        <v>5.129999999999995</v>
+      </c>
+      <c r="H99" t="n">
+        <v>-5.13</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2823,6 +3421,12 @@
       <c r="F100" t="n">
         <v>2.96</v>
       </c>
+      <c r="G100" t="n">
+        <v>4.950000000000003</v>
+      </c>
+      <c r="H100" t="n">
+        <v>-4.95</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2847,6 +3451,12 @@
       <c r="F101" t="n">
         <v>2.71</v>
       </c>
+      <c r="G101" t="n">
+        <v>3.340000000000003</v>
+      </c>
+      <c r="H101" t="n">
+        <v>-3.34</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2871,6 +3481,12 @@
       <c r="F102" t="n">
         <v>3.08</v>
       </c>
+      <c r="G102" t="n">
+        <v>2.570000000000007</v>
+      </c>
+      <c r="H102" t="n">
+        <v>-2.57</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2895,6 +3511,12 @@
       <c r="F103" t="n">
         <v>3.01</v>
       </c>
+      <c r="G103" t="n">
+        <v>6.309999999999988</v>
+      </c>
+      <c r="H103" t="n">
+        <v>-6.31</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2919,6 +3541,12 @@
       <c r="F104" t="n">
         <v>5.96</v>
       </c>
+      <c r="G104" t="n">
+        <v>5.180000000000007</v>
+      </c>
+      <c r="H104" t="n">
+        <v>-5.180000000000001</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2943,6 +3571,12 @@
       <c r="F105" t="n">
         <v>16.03</v>
       </c>
+      <c r="G105" t="n">
+        <v>6.890000000000001</v>
+      </c>
+      <c r="H105" t="n">
+        <v>-6.890000000000001</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2967,6 +3601,12 @@
       <c r="F106" t="n">
         <v>2.08</v>
       </c>
+      <c r="G106" t="n">
+        <v>3.480000000000004</v>
+      </c>
+      <c r="H106" t="n">
+        <v>-3.48</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2991,6 +3631,12 @@
       <c r="F107" t="n">
         <v>49.56</v>
       </c>
+      <c r="G107" t="n">
+        <v>3.879999999999995</v>
+      </c>
+      <c r="H107" t="n">
+        <v>-3.879999999999995</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3015,6 +3661,12 @@
       <c r="F108" t="n">
         <v>47.41</v>
       </c>
+      <c r="G108" t="n">
+        <v>7.370000000000005</v>
+      </c>
+      <c r="H108" t="n">
+        <v>-7.370000000000005</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3039,6 +3691,12 @@
       <c r="F109" t="n">
         <v>47.03</v>
       </c>
+      <c r="G109" t="n">
+        <v>8</v>
+      </c>
+      <c r="H109" t="n">
+        <v>-8</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3063,6 +3721,12 @@
       <c r="F110" t="n">
         <v>51.84</v>
       </c>
+      <c r="G110" t="n">
+        <v>3.609999999999999</v>
+      </c>
+      <c r="H110" t="n">
+        <v>-3.609999999999999</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3087,6 +3751,12 @@
       <c r="F111" t="n">
         <v>65.06999999999999</v>
       </c>
+      <c r="G111" t="n">
+        <v>-2.399999999999999</v>
+      </c>
+      <c r="H111" t="n">
+        <v>2.399999999999991</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3111,6 +3781,12 @@
       <c r="F112" t="n">
         <v>62.54</v>
       </c>
+      <c r="G112" t="n">
+        <v>-3.769999999999996</v>
+      </c>
+      <c r="H112" t="n">
+        <v>3.769999999999996</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3135,6 +3811,12 @@
       <c r="F113" t="n">
         <v>50.89</v>
       </c>
+      <c r="G113" t="n">
+        <v>1.329999999999998</v>
+      </c>
+      <c r="H113" t="n">
+        <v>-1.329999999999998</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3159,6 +3841,12 @@
       <c r="F114" t="n">
         <v>44.46</v>
       </c>
+      <c r="G114" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H114" t="n">
+        <v>-5.75</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3183,6 +3871,12 @@
       <c r="F115" t="n">
         <v>42.38</v>
       </c>
+      <c r="G115" t="n">
+        <v>3.309999999999995</v>
+      </c>
+      <c r="H115" t="n">
+        <v>-3.309999999999995</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3207,6 +3901,12 @@
       <c r="F116" t="n">
         <v>40.73</v>
       </c>
+      <c r="G116" t="n">
+        <v>0.7600000000000051</v>
+      </c>
+      <c r="H116" t="n">
+        <v>-0.7600000000000051</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3231,6 +3931,12 @@
       <c r="F117" t="n">
         <v>37.37</v>
       </c>
+      <c r="G117" t="n">
+        <v>4.390000000000001</v>
+      </c>
+      <c r="H117" t="n">
+        <v>-4.390000000000001</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3255,6 +3961,12 @@
       <c r="F118" t="n">
         <v>32.98</v>
       </c>
+      <c r="G118" t="n">
+        <v>9.009999999999998</v>
+      </c>
+      <c r="H118" t="n">
+        <v>-9.010000000000005</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3279,6 +3991,12 @@
       <c r="F119" t="n">
         <v>23.7</v>
       </c>
+      <c r="G119" t="n">
+        <v>7.730000000000004</v>
+      </c>
+      <c r="H119" t="n">
+        <v>-7.73</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3303,6 +4021,12 @@
       <c r="F120" t="n">
         <v>8.68</v>
       </c>
+      <c r="G120" t="n">
+        <v>1.719999999999999</v>
+      </c>
+      <c r="H120" t="n">
+        <v>-1.720000000000001</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3327,6 +4051,12 @@
       <c r="F121" t="n">
         <v>3.94</v>
       </c>
+      <c r="G121" t="n">
+        <v>1.760000000000005</v>
+      </c>
+      <c r="H121" t="n">
+        <v>-1.76</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3351,6 +4081,12 @@
       <c r="F122" t="n">
         <v>4.11</v>
       </c>
+      <c r="G122" t="n">
+        <v>3.189999999999998</v>
+      </c>
+      <c r="H122" t="n">
+        <v>-3.19</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3375,6 +4111,12 @@
       <c r="F123" t="n">
         <v>3.66</v>
       </c>
+      <c r="G123" t="n">
+        <v>1.870000000000005</v>
+      </c>
+      <c r="H123" t="n">
+        <v>-1.87</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3399,6 +4141,12 @@
       <c r="F124" t="n">
         <v>4.3</v>
       </c>
+      <c r="G124" t="n">
+        <v>0.5799999999999983</v>
+      </c>
+      <c r="H124" t="n">
+        <v>-0.5800000000000001</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3423,6 +4171,12 @@
       <c r="F125" t="n">
         <v>9.1</v>
       </c>
+      <c r="G125" t="n">
+        <v>-1.859999999999999</v>
+      </c>
+      <c r="H125" t="n">
+        <v>1.859999999999999</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3447,6 +4201,12 @@
       <c r="F126" t="n">
         <v>14.62</v>
       </c>
+      <c r="G126" t="n">
+        <v>-9.600000000000009</v>
+      </c>
+      <c r="H126" t="n">
+        <v>9.6</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3471,6 +4231,12 @@
       <c r="F127" t="n">
         <v>6.6</v>
       </c>
+      <c r="G127" t="n">
+        <v>26.73</v>
+      </c>
+      <c r="H127" t="n">
+        <v>-26.73</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3495,6 +4261,12 @@
       <c r="F128" t="n">
         <v>43.77</v>
       </c>
+      <c r="G128" t="n">
+        <v>-4.82</v>
+      </c>
+      <c r="H128" t="n">
+        <v>4.82</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3519,6 +4291,12 @@
       <c r="F129" t="n">
         <v>41.9</v>
       </c>
+      <c r="G129" t="n">
+        <v>-1.960000000000001</v>
+      </c>
+      <c r="H129" t="n">
+        <v>1.960000000000001</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3543,6 +4321,12 @@
       <c r="F130" t="n">
         <v>41.11</v>
       </c>
+      <c r="G130" t="n">
+        <v>1.619999999999997</v>
+      </c>
+      <c r="H130" t="n">
+        <v>-1.619999999999997</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3567,6 +4351,12 @@
       <c r="F131" t="n">
         <v>41.45</v>
       </c>
+      <c r="G131" t="n">
+        <v>-1.160000000000004</v>
+      </c>
+      <c r="H131" t="n">
+        <v>1.160000000000004</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3591,6 +4381,12 @@
       <c r="F132" t="n">
         <v>47.02</v>
       </c>
+      <c r="G132" t="n">
+        <v>-4.450000000000003</v>
+      </c>
+      <c r="H132" t="n">
+        <v>4.450000000000003</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3615,6 +4411,12 @@
       <c r="F133" t="n">
         <v>46.58</v>
       </c>
+      <c r="G133" t="n">
+        <v>-8.469999999999999</v>
+      </c>
+      <c r="H133" t="n">
+        <v>8.469999999999999</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3639,6 +4441,12 @@
       <c r="F134" t="n">
         <v>40.64</v>
       </c>
+      <c r="G134" t="n">
+        <v>-6.450000000000003</v>
+      </c>
+      <c r="H134" t="n">
+        <v>6.450000000000003</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3663,6 +4471,12 @@
       <c r="F135" t="n">
         <v>36.2</v>
       </c>
+      <c r="G135" t="n">
+        <v>-3.040000000000006</v>
+      </c>
+      <c r="H135" t="n">
+        <v>3.040000000000006</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3687,6 +4501,12 @@
       <c r="F136" t="n">
         <v>33.85</v>
       </c>
+      <c r="G136" t="n">
+        <v>-0.009999999999990905</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.00999999999999801</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3711,6 +4531,12 @@
       <c r="F137" t="n">
         <v>32.81</v>
       </c>
+      <c r="G137" t="n">
+        <v>-0.06000000000000227</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.06000000000000227</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3735,6 +4561,12 @@
       <c r="F138" t="n">
         <v>32.44</v>
       </c>
+      <c r="G138" t="n">
+        <v>0.2000000000000028</v>
+      </c>
+      <c r="H138" t="n">
+        <v>-0.2000000000000028</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3759,6 +4591,12 @@
       <c r="F139" t="n">
         <v>30.05</v>
       </c>
+      <c r="G139" t="n">
+        <v>0.2000000000000028</v>
+      </c>
+      <c r="H139" t="n">
+        <v>-0.1999999999999993</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3783,6 +4621,12 @@
       <c r="F140" t="n">
         <v>20.07</v>
       </c>
+      <c r="G140" t="n">
+        <v>0.4200000000000017</v>
+      </c>
+      <c r="H140" t="n">
+        <v>-0.4199999999999982</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3807,6 +4651,12 @@
       <c r="F141" t="n">
         <v>5.79</v>
       </c>
+      <c r="G141" t="n">
+        <v>0.3099999999999881</v>
+      </c>
+      <c r="H141" t="n">
+        <v>-0.3099999999999996</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3831,6 +4681,12 @@
       <c r="F142" t="n">
         <v>2.06</v>
       </c>
+      <c r="G142" t="n">
+        <v>1.049999999999997</v>
+      </c>
+      <c r="H142" t="n">
+        <v>-1.05</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3855,6 +4711,12 @@
       <c r="F143" t="n">
         <v>1.7</v>
       </c>
+      <c r="G143" t="n">
+        <v>1.719999999999999</v>
+      </c>
+      <c r="H143" t="n">
+        <v>-1.72</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3879,6 +4741,12 @@
       <c r="F144" t="n">
         <v>1.63</v>
       </c>
+      <c r="G144" t="n">
+        <v>1.060000000000002</v>
+      </c>
+      <c r="H144" t="n">
+        <v>-1.06</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3903,6 +4771,12 @@
       <c r="F145" t="n">
         <v>1.95</v>
       </c>
+      <c r="G145" t="n">
+        <v>0.2800000000000011</v>
+      </c>
+      <c r="H145" t="n">
+        <v>-0.28</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3927,6 +4801,12 @@
       <c r="F146" t="n">
         <v>4.58</v>
       </c>
+      <c r="G146" t="n">
+        <v>-1.530000000000001</v>
+      </c>
+      <c r="H146" t="n">
+        <v>1.53</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3951,6 +4831,12 @@
       <c r="F147" t="n">
         <v>11.45</v>
       </c>
+      <c r="G147" t="n">
+        <v>-8.400000000000006</v>
+      </c>
+      <c r="H147" t="n">
+        <v>8.399999999999999</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3975,6 +4861,12 @@
       <c r="F148" t="n">
         <v>5.77</v>
       </c>
+      <c r="G148" t="n">
+        <v>-4.019999999999996</v>
+      </c>
+      <c r="H148" t="n">
+        <v>4.02</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3999,6 +4891,12 @@
       <c r="F149" t="n">
         <v>46</v>
       </c>
+      <c r="G149" t="n">
+        <v>-2.600000000000001</v>
+      </c>
+      <c r="H149" t="n">
+        <v>2.600000000000001</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4023,6 +4921,12 @@
       <c r="F150" t="n">
         <v>42.87</v>
       </c>
+      <c r="G150" t="n">
+        <v>0.480000000000004</v>
+      </c>
+      <c r="H150" t="n">
+        <v>-0.480000000000004</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4047,6 +4951,12 @@
       <c r="F151" t="n">
         <v>40.46</v>
       </c>
+      <c r="G151" t="n">
+        <v>3.039999999999999</v>
+      </c>
+      <c r="H151" t="n">
+        <v>-3.039999999999999</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4071,6 +4981,12 @@
       <c r="F152" t="n">
         <v>42.1</v>
       </c>
+      <c r="G152" t="n">
+        <v>2.280000000000001</v>
+      </c>
+      <c r="H152" t="n">
+        <v>-2.280000000000001</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4095,6 +5011,12 @@
       <c r="F153" t="n">
         <v>56.7</v>
       </c>
+      <c r="G153" t="n">
+        <v>-7.010000000000005</v>
+      </c>
+      <c r="H153" t="n">
+        <v>7.010000000000005</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4119,6 +5041,12 @@
       <c r="F154" t="n">
         <v>55.26</v>
       </c>
+      <c r="G154" t="n">
+        <v>-10.82</v>
+      </c>
+      <c r="H154" t="n">
+        <v>10.82</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4143,6 +5071,12 @@
       <c r="F155" t="n">
         <v>42.17</v>
       </c>
+      <c r="G155" t="n">
+        <v>-4.390000000000001</v>
+      </c>
+      <c r="H155" t="n">
+        <v>4.390000000000001</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4167,6 +5101,12 @@
       <c r="F156" t="n">
         <v>36.23</v>
       </c>
+      <c r="G156" t="n">
+        <v>-0.8899999999999935</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0.8899999999999935</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4191,6 +5131,12 @@
       <c r="F157" t="n">
         <v>33.05</v>
       </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4215,6 +5161,12 @@
       <c r="F158" t="n">
         <v>31.71</v>
       </c>
+      <c r="G158" t="n">
+        <v>0.2200000000000131</v>
+      </c>
+      <c r="H158" t="n">
+        <v>-0.2199999999999989</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4239,6 +5191,12 @@
       <c r="F159" t="n">
         <v>29.68</v>
       </c>
+      <c r="G159" t="n">
+        <v>1.129999999999995</v>
+      </c>
+      <c r="H159" t="n">
+        <v>-1.129999999999999</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4263,6 +5221,12 @@
       <c r="F160" t="n">
         <v>26.91</v>
       </c>
+      <c r="G160" t="n">
+        <v>2.710000000000008</v>
+      </c>
+      <c r="H160" t="n">
+        <v>-2.710000000000001</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4287,6 +5251,12 @@
       <c r="F161" t="n">
         <v>18.89</v>
       </c>
+      <c r="G161" t="n">
+        <v>2.299999999999997</v>
+      </c>
+      <c r="H161" t="n">
+        <v>-2.300000000000001</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4311,6 +5281,12 @@
       <c r="F162" t="n">
         <v>6.16</v>
       </c>
+      <c r="G162" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H162" t="n">
+        <v>-0.5</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4335,6 +5311,12 @@
       <c r="F163" t="n">
         <v>2.38</v>
       </c>
+      <c r="G163" t="n">
+        <v>1.300000000000011</v>
+      </c>
+      <c r="H163" t="n">
+        <v>-1.3</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4359,6 +5341,12 @@
       <c r="F164" t="n">
         <v>1.48</v>
       </c>
+      <c r="G164" t="n">
+        <v>1.759999999999991</v>
+      </c>
+      <c r="H164" t="n">
+        <v>-1.76</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4383,6 +5371,12 @@
       <c r="F165" t="n">
         <v>1.31</v>
       </c>
+      <c r="G165" t="n">
+        <v>2.340000000000003</v>
+      </c>
+      <c r="H165" t="n">
+        <v>-2.34</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -4407,6 +5401,12 @@
       <c r="F166" t="n">
         <v>1.76</v>
       </c>
+      <c r="G166" t="n">
+        <v>1.61999999999999</v>
+      </c>
+      <c r="H166" t="n">
+        <v>-1.62</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -4431,6 +5431,12 @@
       <c r="F167" t="n">
         <v>3.19</v>
       </c>
+      <c r="G167" t="n">
+        <v>-0.009999999999990905</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0.009999999999999787</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4455,6 +5461,12 @@
       <c r="F168" t="n">
         <v>5.33</v>
       </c>
+      <c r="G168" t="n">
+        <v>-1.539999999999992</v>
+      </c>
+      <c r="H168" t="n">
+        <v>1.54</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4479,6 +5491,12 @@
       <c r="F169" t="n">
         <v>3.7</v>
       </c>
+      <c r="G169" t="n">
+        <v>6.939999999999998</v>
+      </c>
+      <c r="H169" t="n">
+        <v>-6.94</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -4503,6 +5521,12 @@
       <c r="F170" t="n">
         <v>68.81</v>
       </c>
+      <c r="G170" t="n">
+        <v>0.610000000000003</v>
+      </c>
+      <c r="H170" t="n">
+        <v>-0.6099999999999994</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -4527,6 +5551,12 @@
       <c r="F171" t="n">
         <v>65.62</v>
       </c>
+      <c r="G171" t="n">
+        <v>1.280000000000001</v>
+      </c>
+      <c r="H171" t="n">
+        <v>-1.280000000000001</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -4551,6 +5581,12 @@
       <c r="F172" t="n">
         <v>66.93000000000001</v>
       </c>
+      <c r="G172" t="n">
+        <v>-1.789999999999999</v>
+      </c>
+      <c r="H172" t="n">
+        <v>1.790000000000006</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -4575,6 +5611,12 @@
       <c r="F173" t="n">
         <v>65.56999999999999</v>
       </c>
+      <c r="G173" t="n">
+        <v>-3.189999999999998</v>
+      </c>
+      <c r="H173" t="n">
+        <v>3.189999999999991</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -4599,6 +5641,12 @@
       <c r="F174" t="n">
         <v>79.09999999999999</v>
       </c>
+      <c r="G174" t="n">
+        <v>-7.470000000000002</v>
+      </c>
+      <c r="H174" t="n">
+        <v>7.469999999999999</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -4623,6 +5671,12 @@
       <c r="F175" t="n">
         <v>71.42</v>
       </c>
+      <c r="G175" t="n">
+        <v>-4.560000000000002</v>
+      </c>
+      <c r="H175" t="n">
+        <v>4.560000000000002</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -4647,6 +5701,12 @@
       <c r="F176" t="n">
         <v>60.88</v>
       </c>
+      <c r="G176" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H176" t="n">
+        <v>-1.32</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -4671,6 +5731,12 @@
       <c r="F177" t="n">
         <v>56.66</v>
       </c>
+      <c r="G177" t="n">
+        <v>-0.08999999999999631</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0.08999999999999631</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -4695,6 +5761,12 @@
       <c r="F178" t="n">
         <v>52.54</v>
       </c>
+      <c r="G178" t="n">
+        <v>-3.560000000000002</v>
+      </c>
+      <c r="H178" t="n">
+        <v>3.560000000000002</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -4719,6 +5791,12 @@
       <c r="F179" t="n">
         <v>50.26</v>
       </c>
+      <c r="G179" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H179" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -4743,6 +5821,12 @@
       <c r="F180" t="n">
         <v>46.7</v>
       </c>
+      <c r="G180" t="n">
+        <v>-3.620000000000005</v>
+      </c>
+      <c r="H180" t="n">
+        <v>3.620000000000005</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -4767,6 +5851,12 @@
       <c r="F181" t="n">
         <v>39.65</v>
       </c>
+      <c r="G181" t="n">
+        <v>2.840000000000003</v>
+      </c>
+      <c r="H181" t="n">
+        <v>-2.840000000000003</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -4791,6 +5881,12 @@
       <c r="F182" t="n">
         <v>31.89</v>
       </c>
+      <c r="G182" t="n">
+        <v>5.380000000000003</v>
+      </c>
+      <c r="H182" t="n">
+        <v>-5.380000000000003</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -4815,6 +5911,12 @@
       <c r="F183" t="n">
         <v>17.71</v>
       </c>
+      <c r="G183" t="n">
+        <v>2.280000000000001</v>
+      </c>
+      <c r="H183" t="n">
+        <v>-2.279999999999998</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -4839,6 +5941,12 @@
       <c r="F184" t="n">
         <v>9.77</v>
       </c>
+      <c r="G184" t="n">
+        <v>2.760000000000005</v>
+      </c>
+      <c r="H184" t="n">
+        <v>-2.76</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -4863,6 +5971,12 @@
       <c r="F185" t="n">
         <v>7.84</v>
       </c>
+      <c r="G185" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="H185" t="n">
+        <v>-4.75</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -4887,6 +6001,12 @@
       <c r="F186" t="n">
         <v>5.85</v>
       </c>
+      <c r="G186" t="n">
+        <v>7.730000000000004</v>
+      </c>
+      <c r="H186" t="n">
+        <v>-7.73</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -4911,6 +6031,12 @@
       <c r="F187" t="n">
         <v>6.97</v>
       </c>
+      <c r="G187" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="H187" t="n">
+        <v>-10.03</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -4935,6 +6061,12 @@
       <c r="F188" t="n">
         <v>9.27</v>
       </c>
+      <c r="G188" t="n">
+        <v>12.53</v>
+      </c>
+      <c r="H188" t="n">
+        <v>-12.53</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -4959,6 +6091,12 @@
       <c r="F189" t="n">
         <v>11.28</v>
       </c>
+      <c r="G189" t="n">
+        <v>3.609999999999999</v>
+      </c>
+      <c r="H189" t="n">
+        <v>-3.610000000000001</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -4983,6 +6121,12 @@
       <c r="F190" t="n">
         <v>12.9</v>
       </c>
+      <c r="G190" t="n">
+        <v>17.86999999999999</v>
+      </c>
+      <c r="H190" t="n">
+        <v>-17.87</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -5007,6 +6151,12 @@
       <c r="F191" t="n">
         <v>56.34</v>
       </c>
+      <c r="G191" t="n">
+        <v>-5.460000000000001</v>
+      </c>
+      <c r="H191" t="n">
+        <v>5.460000000000001</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -5031,6 +6181,12 @@
       <c r="F192" t="n">
         <v>49.66</v>
       </c>
+      <c r="G192" t="n">
+        <v>-1.909999999999997</v>
+      </c>
+      <c r="H192" t="n">
+        <v>1.909999999999997</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -5055,6 +6211,12 @@
       <c r="F193" t="n">
         <v>45.74</v>
       </c>
+      <c r="G193" t="n">
+        <v>1.399999999999999</v>
+      </c>
+      <c r="H193" t="n">
+        <v>-1.399999999999999</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -5079,6 +6241,12 @@
       <c r="F194" t="n">
         <v>48.37</v>
       </c>
+      <c r="G194" t="n">
+        <v>-2.449999999999996</v>
+      </c>
+      <c r="H194" t="n">
+        <v>2.449999999999996</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -5103,6 +6271,12 @@
       <c r="F195" t="n">
         <v>68.62</v>
       </c>
+      <c r="G195" t="n">
+        <v>-4.390000000000004</v>
+      </c>
+      <c r="H195" t="n">
+        <v>4.390000000000001</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -5127,6 +6301,12 @@
       <c r="F196" t="n">
         <v>67.86</v>
       </c>
+      <c r="G196" t="n">
+        <v>-7.490000000000002</v>
+      </c>
+      <c r="H196" t="n">
+        <v>7.490000000000002</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -5151,6 +6331,12 @@
       <c r="F197" t="n">
         <v>56.72</v>
       </c>
+      <c r="G197" t="n">
+        <v>-3.339999999999996</v>
+      </c>
+      <c r="H197" t="n">
+        <v>3.339999999999996</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -5175,6 +6361,12 @@
       <c r="F198" t="n">
         <v>48.71</v>
       </c>
+      <c r="G198" t="n">
+        <v>-2.420000000000002</v>
+      </c>
+      <c r="H198" t="n">
+        <v>2.420000000000002</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -5199,6 +6391,12 @@
       <c r="F199" t="n">
         <v>44.55</v>
       </c>
+      <c r="G199" t="n">
+        <v>-2.909999999999997</v>
+      </c>
+      <c r="H199" t="n">
+        <v>2.909999999999997</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -5223,6 +6421,12 @@
       <c r="F200" t="n">
         <v>42.14</v>
       </c>
+      <c r="G200" t="n">
+        <v>-4.75</v>
+      </c>
+      <c r="H200" t="n">
+        <v>4.75</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -5247,6 +6451,12 @@
       <c r="F201" t="n">
         <v>39.71</v>
       </c>
+      <c r="G201" t="n">
+        <v>-3.240000000000002</v>
+      </c>
+      <c r="H201" t="n">
+        <v>3.240000000000002</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -5271,6 +6481,12 @@
       <c r="F202" t="n">
         <v>35.71</v>
       </c>
+      <c r="G202" t="n">
+        <v>0.2200000000000131</v>
+      </c>
+      <c r="H202" t="n">
+        <v>-0.2199999999999989</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -5295,6 +6511,12 @@
       <c r="F203" t="n">
         <v>28.59</v>
       </c>
+      <c r="G203" t="n">
+        <v>0.5499999999999972</v>
+      </c>
+      <c r="H203" t="n">
+        <v>-0.5500000000000007</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -5319,6 +6541,12 @@
       <c r="F204" t="n">
         <v>13.72</v>
       </c>
+      <c r="G204" t="n">
+        <v>-0.6200000000000045</v>
+      </c>
+      <c r="H204" t="n">
+        <v>0.620000000000001</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -5343,6 +6571,12 @@
       <c r="F205" t="n">
         <v>6.41</v>
       </c>
+      <c r="G205" t="n">
+        <v>3.840000000000003</v>
+      </c>
+      <c r="H205" t="n">
+        <v>-3.84</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -5367,6 +6601,12 @@
       <c r="F206" t="n">
         <v>5.33</v>
       </c>
+      <c r="G206" t="n">
+        <v>5.439999999999998</v>
+      </c>
+      <c r="H206" t="n">
+        <v>-5.44</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -5391,6 +6631,12 @@
       <c r="F207" t="n">
         <v>4.37</v>
       </c>
+      <c r="G207" t="n">
+        <v>6.579999999999998</v>
+      </c>
+      <c r="H207" t="n">
+        <v>-6.579999999999999</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -5415,6 +6661,12 @@
       <c r="F208" t="n">
         <v>5.91</v>
       </c>
+      <c r="G208" t="n">
+        <v>5.210000000000008</v>
+      </c>
+      <c r="H208" t="n">
+        <v>-5.209999999999999</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -5439,6 +6691,12 @@
       <c r="F209" t="n">
         <v>8.359999999999999</v>
       </c>
+      <c r="G209" t="n">
+        <v>1.629999999999995</v>
+      </c>
+      <c r="H209" t="n">
+        <v>-1.630000000000001</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -5463,6 +6721,12 @@
       <c r="F210" t="n">
         <v>18.86</v>
       </c>
+      <c r="G210" t="n">
+        <v>-3.140000000000001</v>
+      </c>
+      <c r="H210" t="n">
+        <v>3.139999999999999</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -5487,6 +6751,12 @@
       <c r="F211" t="n">
         <v>13.64</v>
       </c>
+      <c r="G211" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="H211" t="n">
+        <v>-11.36</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -5511,6 +6781,12 @@
       <c r="F212" t="n">
         <v>41.73</v>
       </c>
+      <c r="G212" t="n">
+        <v>-1.049999999999997</v>
+      </c>
+      <c r="H212" t="n">
+        <v>1.049999999999997</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -5535,6 +6811,12 @@
       <c r="F213" t="n">
         <v>37.92</v>
       </c>
+      <c r="G213" t="n">
+        <v>0.3799999999999955</v>
+      </c>
+      <c r="H213" t="n">
+        <v>-0.3799999999999955</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -5559,6 +6841,12 @@
       <c r="F214" t="n">
         <v>38.83</v>
       </c>
+      <c r="G214" t="n">
+        <v>0.07999999999999829</v>
+      </c>
+      <c r="H214" t="n">
+        <v>-0.07999999999999829</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -5583,6 +6871,12 @@
       <c r="F215" t="n">
         <v>39.03</v>
       </c>
+      <c r="G215" t="n">
+        <v>0.03999999999999915</v>
+      </c>
+      <c r="H215" t="n">
+        <v>-0.03999999999999915</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -5607,6 +6901,12 @@
       <c r="F216" t="n">
         <v>50.96</v>
       </c>
+      <c r="G216" t="n">
+        <v>-4.030000000000001</v>
+      </c>
+      <c r="H216" t="n">
+        <v>4.030000000000001</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -5631,6 +6931,12 @@
       <c r="F217" t="n">
         <v>47.99</v>
       </c>
+      <c r="G217" t="n">
+        <v>-5.280000000000001</v>
+      </c>
+      <c r="H217" t="n">
+        <v>5.280000000000001</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -5655,6 +6961,12 @@
       <c r="F218" t="n">
         <v>39.71</v>
       </c>
+      <c r="G218" t="n">
+        <v>-4.990000000000002</v>
+      </c>
+      <c r="H218" t="n">
+        <v>4.990000000000002</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -5679,6 +6991,12 @@
       <c r="F219" t="n">
         <v>33.06</v>
       </c>
+      <c r="G219" t="n">
+        <v>-0.8299999999999983</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0.8300000000000054</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -5703,6 +7021,12 @@
       <c r="F220" t="n">
         <v>30.46</v>
       </c>
+      <c r="G220" t="n">
+        <v>0.210000000000008</v>
+      </c>
+      <c r="H220" t="n">
+        <v>-0.2100000000000009</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -5727,6 +7051,12 @@
       <c r="F221" t="n">
         <v>28.52</v>
       </c>
+      <c r="G221" t="n">
+        <v>1.980000000000004</v>
+      </c>
+      <c r="H221" t="n">
+        <v>-1.98</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -5751,6 +7081,12 @@
       <c r="F222" t="n">
         <v>27.2</v>
       </c>
+      <c r="G222" t="n">
+        <v>1.310000000000002</v>
+      </c>
+      <c r="H222" t="n">
+        <v>-1.310000000000002</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -5775,6 +7111,12 @@
       <c r="F223" t="n">
         <v>26.35</v>
       </c>
+      <c r="G223" t="n">
+        <v>4.350000000000009</v>
+      </c>
+      <c r="H223" t="n">
+        <v>-4.349999999999998</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -5799,6 +7141,12 @@
       <c r="F224" t="n">
         <v>16.9</v>
       </c>
+      <c r="G224" t="n">
+        <v>2.319999999999993</v>
+      </c>
+      <c r="H224" t="n">
+        <v>-2.32</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -5823,6 +7171,12 @@
       <c r="F225" t="n">
         <v>5.55</v>
       </c>
+      <c r="G225" t="n">
+        <v>-0.4699999999999989</v>
+      </c>
+      <c r="H225" t="n">
+        <v>0.4699999999999998</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -5847,6 +7201,12 @@
       <c r="F226" t="n">
         <v>1.42</v>
       </c>
+      <c r="G226" t="n">
+        <v>1.409999999999997</v>
+      </c>
+      <c r="H226" t="n">
+        <v>-1.41</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -5871,6 +7231,12 @@
       <c r="F227" t="n">
         <v>0.85</v>
       </c>
+      <c r="G227" t="n">
+        <v>1.02000000000001</v>
+      </c>
+      <c r="H227" t="n">
+        <v>-1.02</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -5895,6 +7261,12 @@
       <c r="F228" t="n">
         <v>0.71</v>
       </c>
+      <c r="G228" t="n">
+        <v>1.540000000000006</v>
+      </c>
+      <c r="H228" t="n">
+        <v>-1.54</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -5919,6 +7291,12 @@
       <c r="F229" t="n">
         <v>0.58</v>
       </c>
+      <c r="G229" t="n">
+        <v>1.969999999999999</v>
+      </c>
+      <c r="H229" t="n">
+        <v>-1.97</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -5943,6 +7321,12 @@
       <c r="F230" t="n">
         <v>1.03</v>
       </c>
+      <c r="G230" t="n">
+        <v>0.3199999999999932</v>
+      </c>
+      <c r="H230" t="n">
+        <v>-0.3200000000000001</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -5967,6 +7351,12 @@
       <c r="F231" t="n">
         <v>0.93</v>
       </c>
+      <c r="G231" t="n">
+        <v>0.0899999999999892</v>
+      </c>
+      <c r="H231" t="n">
+        <v>-0.08999999999999997</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -5991,6 +7381,12 @@
       <c r="F232" t="n">
         <v>6.25</v>
       </c>
+      <c r="G232" t="n">
+        <v>8.040000000000006</v>
+      </c>
+      <c r="H232" t="n">
+        <v>-8.039999999999999</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -6015,6 +7411,12 @@
       <c r="F233" t="n">
         <v>54.65</v>
       </c>
+      <c r="G233" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H233" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -6039,6 +7441,12 @@
       <c r="F234" t="n">
         <v>49.15</v>
       </c>
+      <c r="G234" t="n">
+        <v>-4.189999999999998</v>
+      </c>
+      <c r="H234" t="n">
+        <v>4.189999999999998</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -6063,6 +7471,12 @@
       <c r="F235" t="n">
         <v>45.83</v>
       </c>
+      <c r="G235" t="n">
+        <v>-5.079999999999998</v>
+      </c>
+      <c r="H235" t="n">
+        <v>5.079999999999998</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -6087,6 +7501,12 @@
       <c r="F236" t="n">
         <v>43.79</v>
       </c>
+      <c r="G236" t="n">
+        <v>-4.799999999999997</v>
+      </c>
+      <c r="H236" t="n">
+        <v>4.799999999999997</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -6111,6 +7531,12 @@
       <c r="F237" t="n">
         <v>60.22</v>
       </c>
+      <c r="G237" t="n">
+        <v>-6.490000000000002</v>
+      </c>
+      <c r="H237" t="n">
+        <v>6.490000000000002</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -6135,6 +7561,12 @@
       <c r="F238" t="n">
         <v>62</v>
       </c>
+      <c r="G238" t="n">
+        <v>-9.920000000000002</v>
+      </c>
+      <c r="H238" t="n">
+        <v>9.920000000000002</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -6159,6 +7591,12 @@
       <c r="F239" t="n">
         <v>51.94</v>
       </c>
+      <c r="G239" t="n">
+        <v>-7.43</v>
+      </c>
+      <c r="H239" t="n">
+        <v>7.43</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -6183,6 +7621,12 @@
       <c r="F240" t="n">
         <v>43.3</v>
       </c>
+      <c r="G240" t="n">
+        <v>-5.519999999999996</v>
+      </c>
+      <c r="H240" t="n">
+        <v>5.519999999999996</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -6207,6 +7651,12 @@
       <c r="F241" t="n">
         <v>37.67</v>
       </c>
+      <c r="G241" t="n">
+        <v>-5.659999999999997</v>
+      </c>
+      <c r="H241" t="n">
+        <v>5.660000000000004</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -6231,6 +7681,12 @@
       <c r="F242" t="n">
         <v>34.39</v>
       </c>
+      <c r="G242" t="n">
+        <v>-7.379999999999995</v>
+      </c>
+      <c r="H242" t="n">
+        <v>7.379999999999999</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -6255,6 +7711,12 @@
       <c r="F243" t="n">
         <v>29.73</v>
       </c>
+      <c r="G243" t="n">
+        <v>-3.700000000000003</v>
+      </c>
+      <c r="H243" t="n">
+        <v>3.699999999999999</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -6279,6 +7741,12 @@
       <c r="F244" t="n">
         <v>25.57</v>
       </c>
+      <c r="G244" t="n">
+        <v>-0.6899999999999977</v>
+      </c>
+      <c r="H244" t="n">
+        <v>0.6900000000000013</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -6303,6 +7771,12 @@
       <c r="F245" t="n">
         <v>20.14</v>
       </c>
+      <c r="G245" t="n">
+        <v>0.9299999999999926</v>
+      </c>
+      <c r="H245" t="n">
+        <v>-0.9299999999999997</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -6327,6 +7801,12 @@
       <c r="F246" t="n">
         <v>7.85</v>
       </c>
+      <c r="G246" t="n">
+        <v>1.350000000000009</v>
+      </c>
+      <c r="H246" t="n">
+        <v>-1.35</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -6351,6 +7831,12 @@
       <c r="F247" t="n">
         <v>3.48</v>
       </c>
+      <c r="G247" t="n">
+        <v>2.86999999999999</v>
+      </c>
+      <c r="H247" t="n">
+        <v>-2.87</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -6375,6 +7861,12 @@
       <c r="F248" t="n">
         <v>3.38</v>
       </c>
+      <c r="G248" t="n">
+        <v>3.02000000000001</v>
+      </c>
+      <c r="H248" t="n">
+        <v>-3.02</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -6399,6 +7891,12 @@
       <c r="F249" t="n">
         <v>2.77</v>
       </c>
+      <c r="G249" t="n">
+        <v>2.700000000000003</v>
+      </c>
+      <c r="H249" t="n">
+        <v>-2.7</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -6423,6 +7921,12 @@
       <c r="F250" t="n">
         <v>2.7</v>
       </c>
+      <c r="G250" t="n">
+        <v>1.859999999999999</v>
+      </c>
+      <c r="H250" t="n">
+        <v>-1.859999999999999</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -6447,6 +7951,12 @@
       <c r="F251" t="n">
         <v>5.48</v>
       </c>
+      <c r="G251" t="n">
+        <v>0.1400000000000006</v>
+      </c>
+      <c r="H251" t="n">
+        <v>-0.1399999999999997</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -6471,6 +7981,12 @@
       <c r="F252" t="n">
         <v>10.6</v>
       </c>
+      <c r="G252" t="n">
+        <v>-4.859999999999999</v>
+      </c>
+      <c r="H252" t="n">
+        <v>4.859999999999999</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -6495,6 +8011,12 @@
       <c r="F253" t="n">
         <v>13.33</v>
       </c>
+      <c r="G253" t="n">
+        <v>1.299999999999997</v>
+      </c>
+      <c r="H253" t="n">
+        <v>-1.300000000000001</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -6519,6 +8041,12 @@
       <c r="F254" t="n">
         <v>48.76</v>
       </c>
+      <c r="G254" t="n">
+        <v>-4.589999999999996</v>
+      </c>
+      <c r="H254" t="n">
+        <v>4.589999999999996</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -6543,6 +8071,12 @@
       <c r="F255" t="n">
         <v>46.61</v>
       </c>
+      <c r="G255" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="H255" t="n">
+        <v>4.25</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -6567,6 +8101,12 @@
       <c r="F256" t="n">
         <v>43.92</v>
       </c>
+      <c r="G256" t="n">
+        <v>-0.5300000000000011</v>
+      </c>
+      <c r="H256" t="n">
+        <v>0.5300000000000011</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -6591,6 +8131,12 @@
       <c r="F257" t="n">
         <v>43.74</v>
       </c>
+      <c r="G257" t="n">
+        <v>1.869999999999997</v>
+      </c>
+      <c r="H257" t="n">
+        <v>-1.869999999999997</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -6615,6 +8161,12 @@
       <c r="F258" t="n">
         <v>56.48</v>
       </c>
+      <c r="G258" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H258" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -6639,6 +8191,12 @@
       <c r="F259" t="n">
         <v>54.68</v>
       </c>
+      <c r="G259" t="n">
+        <v>-10.22</v>
+      </c>
+      <c r="H259" t="n">
+        <v>10.22</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -6663,6 +8221,12 @@
       <c r="F260" t="n">
         <v>45.13</v>
       </c>
+      <c r="G260" t="n">
+        <v>-6.850000000000001</v>
+      </c>
+      <c r="H260" t="n">
+        <v>6.850000000000001</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -6687,6 +8251,12 @@
       <c r="F261" t="n">
         <v>41.6</v>
       </c>
+      <c r="G261" t="n">
+        <v>-5.899999999999999</v>
+      </c>
+      <c r="H261" t="n">
+        <v>5.899999999999999</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -6711,6 +8281,12 @@
       <c r="F262" t="n">
         <v>36.13</v>
       </c>
+      <c r="G262" t="n">
+        <v>-1.149999999999999</v>
+      </c>
+      <c r="H262" t="n">
+        <v>1.150000000000006</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -6735,6 +8311,12 @@
       <c r="F263" t="n">
         <v>34.66</v>
       </c>
+      <c r="G263" t="n">
+        <v>0.3700000000000045</v>
+      </c>
+      <c r="H263" t="n">
+        <v>-0.3700000000000045</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -6759,6 +8341,12 @@
       <c r="F264" t="n">
         <v>33.58</v>
       </c>
+      <c r="G264" t="n">
+        <v>1.920000000000002</v>
+      </c>
+      <c r="H264" t="n">
+        <v>-1.920000000000002</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -6783,6 +8371,12 @@
       <c r="F265" t="n">
         <v>32.55</v>
       </c>
+      <c r="G265" t="n">
+        <v>2.269999999999996</v>
+      </c>
+      <c r="H265" t="n">
+        <v>-2.270000000000003</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -6807,6 +8401,12 @@
       <c r="F266" t="n">
         <v>22.46</v>
       </c>
+      <c r="G266" t="n">
+        <v>0.9700000000000131</v>
+      </c>
+      <c r="H266" t="n">
+        <v>-0.9699999999999989</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -6831,6 +8431,12 @@
       <c r="F267" t="n">
         <v>7.25</v>
       </c>
+      <c r="G267" t="n">
+        <v>0.4200000000000017</v>
+      </c>
+      <c r="H267" t="n">
+        <v>-0.4199999999999999</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -6855,6 +8461,12 @@
       <c r="F268" t="n">
         <v>2.78</v>
       </c>
+      <c r="G268" t="n">
+        <v>0.8199999999999932</v>
+      </c>
+      <c r="H268" t="n">
+        <v>-0.8200000000000003</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -6879,6 +8491,12 @@
       <c r="F269" t="n">
         <v>2.3</v>
       </c>
+      <c r="G269" t="n">
+        <v>0.9099999999999966</v>
+      </c>
+      <c r="H269" t="n">
+        <v>-0.9100000000000001</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -6903,6 +8521,12 @@
       <c r="F270" t="n">
         <v>2.06</v>
       </c>
+      <c r="G270" t="n">
+        <v>0.6099999999999994</v>
+      </c>
+      <c r="H270" t="n">
+        <v>-0.6099999999999999</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -6927,6 +8551,12 @@
       <c r="F271" t="n">
         <v>2.49</v>
       </c>
+      <c r="G271" t="n">
+        <v>-0.06999999999999318</v>
+      </c>
+      <c r="H271" t="n">
+        <v>0.07000000000000028</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -6951,6 +8581,12 @@
       <c r="F272" t="n">
         <v>4.1</v>
       </c>
+      <c r="G272" t="n">
+        <v>-1.009999999999991</v>
+      </c>
+      <c r="H272" t="n">
+        <v>1.01</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -6975,6 +8611,12 @@
       <c r="F273" t="n">
         <v>10.12</v>
       </c>
+      <c r="G273" t="n">
+        <v>-7.670000000000002</v>
+      </c>
+      <c r="H273" t="n">
+        <v>7.669999999999999</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -6999,6 +8641,12 @@
       <c r="F274" t="n">
         <v>13.61</v>
       </c>
+      <c r="G274" t="n">
+        <v>6.730000000000004</v>
+      </c>
+      <c r="H274" t="n">
+        <v>-6.73</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -7023,6 +8671,12 @@
       <c r="F275" t="n">
         <v>57.55</v>
       </c>
+      <c r="G275" t="n">
+        <v>-8.259999999999998</v>
+      </c>
+      <c r="H275" t="n">
+        <v>8.259999999999998</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -7047,6 +8701,12 @@
       <c r="F276" t="n">
         <v>56.58</v>
       </c>
+      <c r="G276" t="n">
+        <v>-7.299999999999997</v>
+      </c>
+      <c r="H276" t="n">
+        <v>7.299999999999997</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -7071,6 +8731,12 @@
       <c r="F277" t="n">
         <v>52.02</v>
       </c>
+      <c r="G277" t="n">
+        <v>-3.010000000000005</v>
+      </c>
+      <c r="H277" t="n">
+        <v>3.010000000000005</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -7095,6 +8761,12 @@
       <c r="F278" t="n">
         <v>53.93</v>
       </c>
+      <c r="G278" t="n">
+        <v>-4.740000000000002</v>
+      </c>
+      <c r="H278" t="n">
+        <v>4.740000000000002</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -7119,6 +8791,12 @@
       <c r="F279" t="n">
         <v>64.44</v>
       </c>
+      <c r="G279" t="n">
+        <v>-8.289999999999999</v>
+      </c>
+      <c r="H279" t="n">
+        <v>8.289999999999999</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -7143,6 +8821,12 @@
       <c r="F280" t="n">
         <v>57.19</v>
       </c>
+      <c r="G280" t="n">
+        <v>-7.659999999999997</v>
+      </c>
+      <c r="H280" t="n">
+        <v>7.659999999999997</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -7167,6 +8851,12 @@
       <c r="F281" t="n">
         <v>51.73</v>
       </c>
+      <c r="G281" t="n">
+        <v>-9.449999999999996</v>
+      </c>
+      <c r="H281" t="n">
+        <v>9.449999999999996</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -7191,6 +8881,12 @@
       <c r="F282" t="n">
         <v>44.02</v>
       </c>
+      <c r="G282" t="n">
+        <v>-3.860000000000007</v>
+      </c>
+      <c r="H282" t="n">
+        <v>3.860000000000007</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -7215,6 +8911,12 @@
       <c r="F283" t="n">
         <v>42.63</v>
       </c>
+      <c r="G283" t="n">
+        <v>-3.920000000000002</v>
+      </c>
+      <c r="H283" t="n">
+        <v>3.920000000000002</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -7239,6 +8941,12 @@
       <c r="F284" t="n">
         <v>38.45</v>
       </c>
+      <c r="G284" t="n">
+        <v>-1.310000000000002</v>
+      </c>
+      <c r="H284" t="n">
+        <v>1.310000000000002</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -7263,6 +8971,12 @@
       <c r="F285" t="n">
         <v>38.76</v>
       </c>
+      <c r="G285" t="n">
+        <v>-1.210000000000001</v>
+      </c>
+      <c r="H285" t="n">
+        <v>1.210000000000001</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -7287,6 +9001,12 @@
       <c r="F286" t="n">
         <v>34.32</v>
       </c>
+      <c r="G286" t="n">
+        <v>2.340000000000003</v>
+      </c>
+      <c r="H286" t="n">
+        <v>-2.339999999999996</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -7311,6 +9031,12 @@
       <c r="F287" t="n">
         <v>28.09</v>
       </c>
+      <c r="G287" t="n">
+        <v>1.36999999999999</v>
+      </c>
+      <c r="H287" t="n">
+        <v>-1.370000000000001</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -7335,6 +9061,12 @@
       <c r="F288" t="n">
         <v>11.54</v>
       </c>
+      <c r="G288" t="n">
+        <v>1.419999999999987</v>
+      </c>
+      <c r="H288" t="n">
+        <v>-1.420000000000002</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -7359,6 +9091,12 @@
       <c r="F289" t="n">
         <v>4.69</v>
       </c>
+      <c r="G289" t="n">
+        <v>3.820000000000007</v>
+      </c>
+      <c r="H289" t="n">
+        <v>-3.819999999999999</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -7383,6 +9121,12 @@
       <c r="F290" t="n">
         <v>3.61</v>
       </c>
+      <c r="G290" t="n">
+        <v>6.390000000000001</v>
+      </c>
+      <c r="H290" t="n">
+        <v>-6.390000000000001</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -7407,6 +9151,12 @@
       <c r="F291" t="n">
         <v>3.83</v>
       </c>
+      <c r="G291" t="n">
+        <v>4.890000000000001</v>
+      </c>
+      <c r="H291" t="n">
+        <v>-4.890000000000001</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -7431,6 +9181,12 @@
       <c r="F292" t="n">
         <v>4.59</v>
       </c>
+      <c r="G292" t="n">
+        <v>3.269999999999996</v>
+      </c>
+      <c r="H292" t="n">
+        <v>-3.27</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -7455,6 +9211,12 @@
       <c r="F293" t="n">
         <v>9.49</v>
       </c>
+      <c r="G293" t="n">
+        <v>3.980000000000004</v>
+      </c>
+      <c r="H293" t="n">
+        <v>-3.98</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -7479,6 +9241,12 @@
       <c r="F294" t="n">
         <v>15.71</v>
       </c>
+      <c r="G294" t="n">
+        <v>2.870000000000005</v>
+      </c>
+      <c r="H294" t="n">
+        <v>-2.869999999999997</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -7503,6 +9271,12 @@
       <c r="F295" t="n">
         <v>17.33</v>
       </c>
+      <c r="G295" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="H295" t="n">
+        <v>-39.39</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -7527,6 +9301,12 @@
       <c r="F296" t="n">
         <v>37.23</v>
       </c>
+      <c r="G296" t="n">
+        <v>2.550000000000004</v>
+      </c>
+      <c r="H296" t="n">
+        <v>-2.550000000000004</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -7551,6 +9331,12 @@
       <c r="F297" t="n">
         <v>34.47</v>
       </c>
+      <c r="G297" t="n">
+        <v>-0.6500000000000057</v>
+      </c>
+      <c r="H297" t="n">
+        <v>0.6499999999999986</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -7575,6 +9361,12 @@
       <c r="F298" t="n">
         <v>31.46</v>
       </c>
+      <c r="G298" t="n">
+        <v>3.870000000000005</v>
+      </c>
+      <c r="H298" t="n">
+        <v>-3.869999999999997</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -7599,6 +9391,12 @@
       <c r="F299" t="n">
         <v>33.71</v>
       </c>
+      <c r="G299" t="n">
+        <v>4.920000000000009</v>
+      </c>
+      <c r="H299" t="n">
+        <v>-4.920000000000002</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -7623,6 +9421,12 @@
       <c r="F300" t="n">
         <v>49.96</v>
       </c>
+      <c r="G300" t="n">
+        <v>1.439999999999998</v>
+      </c>
+      <c r="H300" t="n">
+        <v>-1.439999999999998</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -7647,6 +9451,12 @@
       <c r="F301" t="n">
         <v>46.04</v>
       </c>
+      <c r="G301" t="n">
+        <v>-5.519999999999996</v>
+      </c>
+      <c r="H301" t="n">
+        <v>5.519999999999996</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -7671,6 +9481,12 @@
       <c r="F302" t="n">
         <v>35.61</v>
       </c>
+      <c r="G302" t="n">
+        <v>-2.329999999999998</v>
+      </c>
+      <c r="H302" t="n">
+        <v>2.329999999999998</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -7695,6 +9511,12 @@
       <c r="F303" t="n">
         <v>30.36</v>
       </c>
+      <c r="G303" t="n">
+        <v>0.9300000000000068</v>
+      </c>
+      <c r="H303" t="n">
+        <v>-0.9299999999999997</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -7719,6 +9541,12 @@
       <c r="F304" t="n">
         <v>28.79</v>
       </c>
+      <c r="G304" t="n">
+        <v>1.839999999999989</v>
+      </c>
+      <c r="H304" t="n">
+        <v>-1.84</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -7743,6 +9571,12 @@
       <c r="F305" t="n">
         <v>28.45</v>
       </c>
+      <c r="G305" t="n">
+        <v>1.489999999999995</v>
+      </c>
+      <c r="H305" t="n">
+        <v>-1.490000000000002</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -7767,6 +9601,12 @@
       <c r="F306" t="n">
         <v>28.11</v>
       </c>
+      <c r="G306" t="n">
+        <v>4.040000000000006</v>
+      </c>
+      <c r="H306" t="n">
+        <v>-4.039999999999999</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -7791,6 +9631,12 @@
       <c r="F307" t="n">
         <v>27.76</v>
       </c>
+      <c r="G307" t="n">
+        <v>4.859999999999999</v>
+      </c>
+      <c r="H307" t="n">
+        <v>-4.859999999999996</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -7815,6 +9661,12 @@
       <c r="F308" t="n">
         <v>22.44</v>
       </c>
+      <c r="G308" t="n">
+        <v>4.510000000000005</v>
+      </c>
+      <c r="H308" t="n">
+        <v>-4.509999999999998</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -7839,6 +9691,12 @@
       <c r="F309" t="n">
         <v>10.21</v>
       </c>
+      <c r="G309" t="n">
+        <v>4.560000000000002</v>
+      </c>
+      <c r="H309" t="n">
+        <v>-4.559999999999999</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -7863,6 +9721,12 @@
       <c r="F310" t="n">
         <v>4.34</v>
       </c>
+      <c r="G310" t="n">
+        <v>5.439999999999998</v>
+      </c>
+      <c r="H310" t="n">
+        <v>-5.44</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -7887,6 +9751,12 @@
       <c r="F311" t="n">
         <v>3.48</v>
       </c>
+      <c r="G311" t="n">
+        <v>5.519999999999996</v>
+      </c>
+      <c r="H311" t="n">
+        <v>-5.52</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -7911,6 +9781,12 @@
       <c r="F312" t="n">
         <v>2.5</v>
       </c>
+      <c r="G312" t="n">
+        <v>4.099999999999994</v>
+      </c>
+      <c r="H312" t="n">
+        <v>-4.1</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -7935,6 +9811,12 @@
       <c r="F313" t="n">
         <v>2.81</v>
       </c>
+      <c r="G313" t="n">
+        <v>3.069999999999993</v>
+      </c>
+      <c r="H313" t="n">
+        <v>-3.07</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -7959,6 +9841,12 @@
       <c r="F314" t="n">
         <v>6.91</v>
       </c>
+      <c r="G314" t="n">
+        <v>3.810000000000002</v>
+      </c>
+      <c r="H314" t="n">
+        <v>-3.81</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -7983,6 +9871,12 @@
       <c r="F315" t="n">
         <v>6.55</v>
       </c>
+      <c r="G315" t="n">
+        <v>6.469999999999999</v>
+      </c>
+      <c r="H315" t="n">
+        <v>-6.47</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -8007,6 +9901,12 @@
       <c r="F316" t="n">
         <v>7.69</v>
       </c>
+      <c r="G316" t="n">
+        <v>44.16</v>
+      </c>
+      <c r="H316" t="n">
+        <v>-44.16</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -8031,6 +9931,12 @@
       <c r="F317" t="n">
         <v>42.37</v>
       </c>
+      <c r="G317" t="n">
+        <v>-3.439999999999998</v>
+      </c>
+      <c r="H317" t="n">
+        <v>3.439999999999998</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -8055,6 +9961,12 @@
       <c r="F318" t="n">
         <v>37.33</v>
       </c>
+      <c r="G318" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="H318" t="n">
+        <v>1.18</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -8079,6 +9991,12 @@
       <c r="F319" t="n">
         <v>35.5</v>
       </c>
+      <c r="G319" t="n">
+        <v>-1.950000000000003</v>
+      </c>
+      <c r="H319" t="n">
+        <v>1.950000000000003</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -8103,6 +10021,12 @@
       <c r="F320" t="n">
         <v>37.67</v>
       </c>
+      <c r="G320" t="n">
+        <v>1.460000000000001</v>
+      </c>
+      <c r="H320" t="n">
+        <v>-1.460000000000001</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -8127,6 +10051,12 @@
       <c r="F321" t="n">
         <v>57</v>
       </c>
+      <c r="G321" t="n">
+        <v>-4.880000000000003</v>
+      </c>
+      <c r="H321" t="n">
+        <v>4.880000000000003</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -8151,6 +10081,12 @@
       <c r="F322" t="n">
         <v>52.64</v>
       </c>
+      <c r="G322" t="n">
+        <v>-9.829999999999998</v>
+      </c>
+      <c r="H322" t="n">
+        <v>9.829999999999998</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -8175,6 +10111,12 @@
       <c r="F323" t="n">
         <v>41.87</v>
       </c>
+      <c r="G323" t="n">
+        <v>-6.889999999999993</v>
+      </c>
+      <c r="H323" t="n">
+        <v>6.890000000000001</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -8199,6 +10141,12 @@
       <c r="F324" t="n">
         <v>34.96</v>
       </c>
+      <c r="G324" t="n">
+        <v>-0.7199999999999989</v>
+      </c>
+      <c r="H324" t="n">
+        <v>0.7199999999999989</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -8223,6 +10171,12 @@
       <c r="F325" t="n">
         <v>32.26</v>
       </c>
+      <c r="G325" t="n">
+        <v>0.03000000000000114</v>
+      </c>
+      <c r="H325" t="n">
+        <v>-0.03000000000000114</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -8247,6 +10201,12 @@
       <c r="F326" t="n">
         <v>31.75</v>
       </c>
+      <c r="G326" t="n">
+        <v>-1.709999999999994</v>
+      </c>
+      <c r="H326" t="n">
+        <v>1.710000000000001</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -8271,6 +10231,12 @@
       <c r="F327" t="n">
         <v>31.89</v>
       </c>
+      <c r="G327" t="n">
+        <v>-0.06000000000000227</v>
+      </c>
+      <c r="H327" t="n">
+        <v>0.06000000000000227</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -8295,6 +10261,12 @@
       <c r="F328" t="n">
         <v>30.84</v>
       </c>
+      <c r="G328" t="n">
+        <v>-0.230000000000004</v>
+      </c>
+      <c r="H328" t="n">
+        <v>0.2300000000000004</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -8319,6 +10291,12 @@
       <c r="F329" t="n">
         <v>21.31</v>
       </c>
+      <c r="G329" t="n">
+        <v>3.439999999999998</v>
+      </c>
+      <c r="H329" t="n">
+        <v>-3.440000000000001</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -8343,6 +10321,12 @@
       <c r="F330" t="n">
         <v>7.16</v>
       </c>
+      <c r="G330" t="n">
+        <v>4.480000000000004</v>
+      </c>
+      <c r="H330" t="n">
+        <v>-4.48</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -8367,6 +10351,12 @@
       <c r="F331" t="n">
         <v>2.88</v>
       </c>
+      <c r="G331" t="n">
+        <v>4.329999999999998</v>
+      </c>
+      <c r="H331" t="n">
+        <v>-4.33</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -8391,6 +10381,12 @@
       <c r="F332" t="n">
         <v>2.79</v>
       </c>
+      <c r="G332" t="n">
+        <v>4.129999999999995</v>
+      </c>
+      <c r="H332" t="n">
+        <v>-4.13</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -8415,6 +10411,12 @@
       <c r="F333" t="n">
         <v>2.78</v>
       </c>
+      <c r="G333" t="n">
+        <v>3.959999999999994</v>
+      </c>
+      <c r="H333" t="n">
+        <v>-3.96</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -8439,6 +10441,12 @@
       <c r="F334" t="n">
         <v>2.41</v>
       </c>
+      <c r="G334" t="n">
+        <v>3.790000000000006</v>
+      </c>
+      <c r="H334" t="n">
+        <v>-3.79</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -8463,6 +10471,12 @@
       <c r="F335" t="n">
         <v>6.63</v>
       </c>
+      <c r="G335" t="n">
+        <v>-1.170000000000002</v>
+      </c>
+      <c r="H335" t="n">
+        <v>1.17</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -8487,6 +10501,12 @@
       <c r="F336" t="n">
         <v>14.98</v>
       </c>
+      <c r="G336" t="n">
+        <v>-6.680000000000007</v>
+      </c>
+      <c r="H336" t="n">
+        <v>6.68</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -8511,6 +10531,12 @@
       <c r="F337" t="n">
         <v>10.75</v>
       </c>
+      <c r="G337" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="H337" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -8535,6 +10561,12 @@
       <c r="F338" t="n">
         <v>60.04</v>
       </c>
+      <c r="G338" t="n">
+        <v>-4.079999999999998</v>
+      </c>
+      <c r="H338" t="n">
+        <v>4.079999999999998</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -8559,6 +10591,12 @@
       <c r="F339" t="n">
         <v>54.61</v>
       </c>
+      <c r="G339" t="n">
+        <v>-1.890000000000001</v>
+      </c>
+      <c r="H339" t="n">
+        <v>1.890000000000001</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -8583,6 +10621,12 @@
       <c r="F340" t="n">
         <v>51.11</v>
       </c>
+      <c r="G340" t="n">
+        <v>0.6799999999999997</v>
+      </c>
+      <c r="H340" t="n">
+        <v>-0.6799999999999997</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -8607,6 +10651,12 @@
       <c r="F341" t="n">
         <v>52.4</v>
       </c>
+      <c r="G341" t="n">
+        <v>-0.6400000000000006</v>
+      </c>
+      <c r="H341" t="n">
+        <v>0.6400000000000006</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -8631,6 +10681,12 @@
       <c r="F342" t="n">
         <v>65.34999999999999</v>
       </c>
+      <c r="G342" t="n">
+        <v>-2.950000000000003</v>
+      </c>
+      <c r="H342" t="n">
+        <v>2.949999999999996</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -8655,6 +10711,12 @@
       <c r="F343" t="n">
         <v>65.06999999999999</v>
       </c>
+      <c r="G343" t="n">
+        <v>-6.590000000000003</v>
+      </c>
+      <c r="H343" t="n">
+        <v>6.589999999999996</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -8679,6 +10741,12 @@
       <c r="F344" t="n">
         <v>54.65</v>
       </c>
+      <c r="G344" t="n">
+        <v>-2.710000000000001</v>
+      </c>
+      <c r="H344" t="n">
+        <v>2.710000000000001</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -8703,6 +10771,12 @@
       <c r="F345" t="n">
         <v>47.16</v>
       </c>
+      <c r="G345" t="n">
+        <v>-0.9599999999999937</v>
+      </c>
+      <c r="H345" t="n">
+        <v>0.9599999999999937</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -8727,6 +10801,12 @@
       <c r="F346" t="n">
         <v>43.95</v>
       </c>
+      <c r="G346" t="n">
+        <v>-1.450000000000003</v>
+      </c>
+      <c r="H346" t="n">
+        <v>1.450000000000003</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -8751,6 +10831,12 @@
       <c r="F347" t="n">
         <v>42.27</v>
       </c>
+      <c r="G347" t="n">
+        <v>-0.7900000000000063</v>
+      </c>
+      <c r="H347" t="n">
+        <v>0.7900000000000063</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -8775,6 +10861,12 @@
       <c r="F348" t="n">
         <v>40.48</v>
       </c>
+      <c r="G348" t="n">
+        <v>0.5900000000000034</v>
+      </c>
+      <c r="H348" t="n">
+        <v>-0.5900000000000034</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -8799,6 +10891,12 @@
       <c r="F349" t="n">
         <v>38.65</v>
       </c>
+      <c r="G349" t="n">
+        <v>0.1900000000000048</v>
+      </c>
+      <c r="H349" t="n">
+        <v>-0.1900000000000048</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -8823,6 +10921,12 @@
       <c r="F350" t="n">
         <v>30.69</v>
       </c>
+      <c r="G350" t="n">
+        <v>-1.209999999999994</v>
+      </c>
+      <c r="H350" t="n">
+        <v>1.210000000000001</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -8847,6 +10951,12 @@
       <c r="F351" t="n">
         <v>13.6</v>
       </c>
+      <c r="G351" t="n">
+        <v>-1.439999999999998</v>
+      </c>
+      <c r="H351" t="n">
+        <v>1.44</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -8871,6 +10981,12 @@
       <c r="F352" t="n">
         <v>6.85</v>
       </c>
+      <c r="G352" t="n">
+        <v>1.930000000000007</v>
+      </c>
+      <c r="H352" t="n">
+        <v>-1.93</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -8895,6 +11011,12 @@
       <c r="F353" t="n">
         <v>5.21</v>
       </c>
+      <c r="G353" t="n">
+        <v>2.650000000000006</v>
+      </c>
+      <c r="H353" t="n">
+        <v>-2.65</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -8919,6 +11041,12 @@
       <c r="F354" t="n">
         <v>5.28</v>
       </c>
+      <c r="G354" t="n">
+        <v>1.920000000000002</v>
+      </c>
+      <c r="H354" t="n">
+        <v>-1.92</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -8943,6 +11071,12 @@
       <c r="F355" t="n">
         <v>5.34</v>
       </c>
+      <c r="G355" t="n">
+        <v>1.049999999999997</v>
+      </c>
+      <c r="H355" t="n">
+        <v>-1.05</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -8967,6 +11101,12 @@
       <c r="F356" t="n">
         <v>9.68</v>
       </c>
+      <c r="G356" t="n">
+        <v>-2.610000000000014</v>
+      </c>
+      <c r="H356" t="n">
+        <v>2.609999999999999</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -8991,6 +11131,12 @@
       <c r="F357" t="n">
         <v>21.46</v>
       </c>
+      <c r="G357" t="n">
+        <v>-18.34999999999999</v>
+      </c>
+      <c r="H357" t="n">
+        <v>18.35</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -9015,6 +11161,12 @@
       <c r="F358" t="n">
         <v>17.5</v>
       </c>
+      <c r="G358" t="n">
+        <v>1.489999999999995</v>
+      </c>
+      <c r="H358" t="n">
+        <v>-1.489999999999998</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -9039,6 +11191,12 @@
       <c r="F359" t="n">
         <v>55.57</v>
       </c>
+      <c r="G359" t="n">
+        <v>-2.840000000000003</v>
+      </c>
+      <c r="H359" t="n">
+        <v>2.840000000000003</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -9063,6 +11221,12 @@
       <c r="F360" t="n">
         <v>52.02</v>
       </c>
+      <c r="G360" t="n">
+        <v>-2.190000000000005</v>
+      </c>
+      <c r="H360" t="n">
+        <v>2.190000000000005</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -9087,6 +11251,12 @@
       <c r="F361" t="n">
         <v>46.24</v>
       </c>
+      <c r="G361" t="n">
+        <v>2.739999999999995</v>
+      </c>
+      <c r="H361" t="n">
+        <v>-2.739999999999995</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -9111,6 +11281,12 @@
       <c r="F362" t="n">
         <v>50.87</v>
       </c>
+      <c r="G362" t="n">
+        <v>-1.579999999999998</v>
+      </c>
+      <c r="H362" t="n">
+        <v>1.579999999999998</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -9135,6 +11311,12 @@
       <c r="F363" t="n">
         <v>65.81999999999999</v>
       </c>
+      <c r="G363" t="n">
+        <v>-4.880000000000003</v>
+      </c>
+      <c r="H363" t="n">
+        <v>4.879999999999995</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -9159,6 +11341,12 @@
       <c r="F364" t="n">
         <v>62.49</v>
       </c>
+      <c r="G364" t="n">
+        <v>-9.580000000000005</v>
+      </c>
+      <c r="H364" t="n">
+        <v>9.580000000000005</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -9183,6 +11371,12 @@
       <c r="F365" t="n">
         <v>51.26</v>
       </c>
+      <c r="G365" t="n">
+        <v>-3.710000000000001</v>
+      </c>
+      <c r="H365" t="n">
+        <v>3.710000000000001</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -9207,6 +11401,12 @@
       <c r="F366" t="n">
         <v>45.16</v>
       </c>
+      <c r="G366" t="n">
+        <v>-2.309999999999995</v>
+      </c>
+      <c r="H366" t="n">
+        <v>2.309999999999995</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -9231,6 +11431,12 @@
       <c r="F367" t="n">
         <v>42.57</v>
       </c>
+      <c r="G367" t="n">
+        <v>-2.990000000000002</v>
+      </c>
+      <c r="H367" t="n">
+        <v>2.990000000000002</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -9255,6 +11461,12 @@
       <c r="F368" t="n">
         <v>41.21</v>
       </c>
+      <c r="G368" t="n">
+        <v>-2.550000000000004</v>
+      </c>
+      <c r="H368" t="n">
+        <v>2.550000000000004</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -9279,6 +11491,12 @@
       <c r="F369" t="n">
         <v>38.8</v>
       </c>
+      <c r="G369" t="n">
+        <v>-0.8999999999999986</v>
+      </c>
+      <c r="H369" t="n">
+        <v>0.8999999999999986</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -9303,6 +11521,12 @@
       <c r="F370" t="n">
         <v>37.12</v>
       </c>
+      <c r="G370" t="n">
+        <v>-1.130000000000003</v>
+      </c>
+      <c r="H370" t="n">
+        <v>1.129999999999995</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -9327,6 +11551,12 @@
       <c r="F371" t="n">
         <v>25.9</v>
       </c>
+      <c r="G371" t="n">
+        <v>2.289999999999992</v>
+      </c>
+      <c r="H371" t="n">
+        <v>-2.290000000000003</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -9351,6 +11581,12 @@
       <c r="F372" t="n">
         <v>9.050000000000001</v>
       </c>
+      <c r="G372" t="n">
+        <v>0.5600000000000023</v>
+      </c>
+      <c r="H372" t="n">
+        <v>-0.5599999999999987</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -9375,6 +11611,12 @@
       <c r="F373" t="n">
         <v>2.87</v>
       </c>
+      <c r="G373" t="n">
+        <v>3.060000000000002</v>
+      </c>
+      <c r="H373" t="n">
+        <v>-3.06</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -9399,6 +11641,12 @@
       <c r="F374" t="n">
         <v>2.38</v>
       </c>
+      <c r="G374" t="n">
+        <v>4.560000000000002</v>
+      </c>
+      <c r="H374" t="n">
+        <v>-4.56</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -9423,6 +11671,12 @@
       <c r="F375" t="n">
         <v>2.39</v>
       </c>
+      <c r="G375" t="n">
+        <v>1.439999999999998</v>
+      </c>
+      <c r="H375" t="n">
+        <v>-1.44</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -9447,6 +11701,12 @@
       <c r="F376" t="n">
         <v>2.95</v>
       </c>
+      <c r="G376" t="n">
+        <v>-0.7400000000000091</v>
+      </c>
+      <c r="H376" t="n">
+        <v>0.7400000000000002</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -9471,6 +11731,12 @@
       <c r="F377" t="n">
         <v>5.56</v>
       </c>
+      <c r="G377" t="n">
+        <v>-1.480000000000004</v>
+      </c>
+      <c r="H377" t="n">
+        <v>1.48</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -9495,6 +11761,12 @@
       <c r="F378" t="n">
         <v>10.04</v>
       </c>
+      <c r="G378" t="n">
+        <v>0.289999999999992</v>
+      </c>
+      <c r="H378" t="n">
+        <v>-0.2900000000000009</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -9519,6 +11791,12 @@
       <c r="F379" t="n">
         <v>7.41</v>
       </c>
+      <c r="G379" t="n">
+        <v>4.350000000000009</v>
+      </c>
+      <c r="H379" t="n">
+        <v>-4.35</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -9543,6 +11821,12 @@
       <c r="F380" t="n">
         <v>45.52</v>
       </c>
+      <c r="G380" t="n">
+        <v>0.4499999999999957</v>
+      </c>
+      <c r="H380" t="n">
+        <v>-0.4499999999999957</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -9567,6 +11851,12 @@
       <c r="F381" t="n">
         <v>40.91</v>
       </c>
+      <c r="G381" t="n">
+        <v>5.080000000000005</v>
+      </c>
+      <c r="H381" t="n">
+        <v>-5.080000000000005</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -9591,6 +11881,12 @@
       <c r="F382" t="n">
         <v>38.71</v>
       </c>
+      <c r="G382" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="H382" t="n">
+        <v>-10.57</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -9615,6 +11911,12 @@
       <c r="F383" t="n">
         <v>43.83</v>
       </c>
+      <c r="G383" t="n">
+        <v>8.410000000000004</v>
+      </c>
+      <c r="H383" t="n">
+        <v>-8.410000000000004</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -9639,6 +11941,12 @@
       <c r="F384" t="n">
         <v>60.28</v>
       </c>
+      <c r="G384" t="n">
+        <v>-3.939999999999998</v>
+      </c>
+      <c r="H384" t="n">
+        <v>3.939999999999998</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -9663,6 +11971,12 @@
       <c r="F385" t="n">
         <v>55.77</v>
       </c>
+      <c r="G385" t="n">
+        <v>-12.39</v>
+      </c>
+      <c r="H385" t="n">
+        <v>12.39</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -9687,6 +12001,12 @@
       <c r="F386" t="n">
         <v>44.38</v>
       </c>
+      <c r="G386" t="n">
+        <v>-8.970000000000006</v>
+      </c>
+      <c r="H386" t="n">
+        <v>8.970000000000006</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -9711,6 +12031,12 @@
       <c r="F387" t="n">
         <v>34.26</v>
       </c>
+      <c r="G387" t="n">
+        <v>1.469999999999999</v>
+      </c>
+      <c r="H387" t="n">
+        <v>-1.469999999999999</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -9735,6 +12061,12 @@
       <c r="F388" t="n">
         <v>29.54</v>
       </c>
+      <c r="G388" t="n">
+        <v>8.669999999999995</v>
+      </c>
+      <c r="H388" t="n">
+        <v>-8.670000000000002</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -9759,6 +12091,12 @@
       <c r="F389" t="n">
         <v>32.52</v>
       </c>
+      <c r="G389" t="n">
+        <v>1.760000000000005</v>
+      </c>
+      <c r="H389" t="n">
+        <v>-1.759999999999998</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -9783,6 +12121,12 @@
       <c r="F390" t="n">
         <v>32.58</v>
       </c>
+      <c r="G390" t="n">
+        <v>3.980000000000004</v>
+      </c>
+      <c r="H390" t="n">
+        <v>-3.980000000000004</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -9807,6 +12151,12 @@
       <c r="F391" t="n">
         <v>31.02</v>
       </c>
+      <c r="G391" t="n">
+        <v>3.299999999999997</v>
+      </c>
+      <c r="H391" t="n">
+        <v>-3.300000000000001</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -9831,6 +12181,12 @@
       <c r="F392" t="n">
         <v>23.23</v>
       </c>
+      <c r="G392" t="n">
+        <v>0.2000000000000028</v>
+      </c>
+      <c r="H392" t="n">
+        <v>-0.1999999999999993</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -9855,6 +12211,12 @@
       <c r="F393" t="n">
         <v>7.12</v>
       </c>
+      <c r="G393" t="n">
+        <v>1.699999999999989</v>
+      </c>
+      <c r="H393" t="n">
+        <v>-1.7</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -9879,6 +12241,12 @@
       <c r="F394" t="n">
         <v>2</v>
       </c>
+      <c r="G394" t="n">
+        <v>2.810000000000002</v>
+      </c>
+      <c r="H394" t="n">
+        <v>-2.81</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -9903,6 +12271,12 @@
       <c r="F395" t="n">
         <v>1.46</v>
       </c>
+      <c r="G395" t="n">
+        <v>3.200000000000003</v>
+      </c>
+      <c r="H395" t="n">
+        <v>-3.2</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -9927,6 +12301,12 @@
       <c r="F396" t="n">
         <v>1.43</v>
       </c>
+      <c r="G396" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H396" t="n">
+        <v>-2.75</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -9951,6 +12331,12 @@
       <c r="F397" t="n">
         <v>2.32</v>
       </c>
+      <c r="G397" t="n">
+        <v>2.050000000000011</v>
+      </c>
+      <c r="H397" t="n">
+        <v>-2.05</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -9975,6 +12361,12 @@
       <c r="F398" t="n">
         <v>3.95</v>
       </c>
+      <c r="G398" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="H398" t="n">
+        <v>-4.249999999999999</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -9999,6 +12391,12 @@
       <c r="F399" t="n">
         <v>6.69</v>
       </c>
+      <c r="G399" t="n">
+        <v>0.5400000000000063</v>
+      </c>
+      <c r="H399" t="n">
+        <v>-0.54</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -10023,6 +12421,12 @@
       <c r="F400" t="n">
         <v>2.5</v>
       </c>
+      <c r="G400" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H400" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -10047,6 +12451,12 @@
       <c r="F401" t="n">
         <v>16.15</v>
       </c>
+      <c r="G401" t="n">
+        <v>0.6799999999999926</v>
+      </c>
+      <c r="H401" t="n">
+        <v>-0.6799999999999997</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -10071,6 +12481,12 @@
       <c r="F402" t="n">
         <v>13.37</v>
       </c>
+      <c r="G402" t="n">
+        <v>1.170000000000002</v>
+      </c>
+      <c r="H402" t="n">
+        <v>-1.17</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -10095,6 +12511,12 @@
       <c r="F403" t="n">
         <v>12.4</v>
       </c>
+      <c r="G403" t="n">
+        <v>0.3299999999999983</v>
+      </c>
+      <c r="H403" t="n">
+        <v>-0.3300000000000001</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -10119,6 +12541,12 @@
       <c r="F404" t="n">
         <v>16.18</v>
       </c>
+      <c r="G404" t="n">
+        <v>3.389999999999986</v>
+      </c>
+      <c r="H404" t="n">
+        <v>-3.390000000000001</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -10143,6 +12571,12 @@
       <c r="F405" t="n">
         <v>39.17</v>
       </c>
+      <c r="G405" t="n">
+        <v>-5.670000000000002</v>
+      </c>
+      <c r="H405" t="n">
+        <v>5.670000000000002</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -10167,6 +12601,12 @@
       <c r="F406" t="n">
         <v>31.72</v>
       </c>
+      <c r="G406" t="n">
+        <v>-9.709999999999994</v>
+      </c>
+      <c r="H406" t="n">
+        <v>9.709999999999997</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -10191,6 +12631,12 @@
       <c r="F407" t="n">
         <v>20.65</v>
       </c>
+      <c r="G407" t="n">
+        <v>-4.170000000000002</v>
+      </c>
+      <c r="H407" t="n">
+        <v>4.169999999999998</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -10215,6 +12661,12 @@
       <c r="F408" t="n">
         <v>15.81</v>
       </c>
+      <c r="G408" t="n">
+        <v>-0.7800000000000011</v>
+      </c>
+      <c r="H408" t="n">
+        <v>0.7800000000000011</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -10239,6 +12691,12 @@
       <c r="F409" t="n">
         <v>14.31</v>
       </c>
+      <c r="G409" t="n">
+        <v>0.1799999999999926</v>
+      </c>
+      <c r="H409" t="n">
+        <v>-0.1799999999999997</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -10263,6 +12721,12 @@
       <c r="F410" t="n">
         <v>14.11</v>
       </c>
+      <c r="G410" t="n">
+        <v>-3.840000000000003</v>
+      </c>
+      <c r="H410" t="n">
+        <v>3.84</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -10287,6 +12751,12 @@
       <c r="F411" t="n">
         <v>13.49</v>
       </c>
+      <c r="G411" t="n">
+        <v>0.9100000000000108</v>
+      </c>
+      <c r="H411" t="n">
+        <v>-0.9100000000000001</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -10311,6 +12781,12 @@
       <c r="F412" t="n">
         <v>13.85</v>
       </c>
+      <c r="G412" t="n">
+        <v>1.260000000000005</v>
+      </c>
+      <c r="H412" t="n">
+        <v>-1.26</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -10335,6 +12811,12 @@
       <c r="F413" t="n">
         <v>7.54</v>
       </c>
+      <c r="G413" t="n">
+        <v>7.089999999999989</v>
+      </c>
+      <c r="H413" t="n">
+        <v>-7.090000000000001</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -10359,6 +12841,12 @@
       <c r="F414" t="n">
         <v>3.64</v>
       </c>
+      <c r="G414" t="n">
+        <v>4.239999999999995</v>
+      </c>
+      <c r="H414" t="n">
+        <v>-4.24</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -10383,6 +12871,12 @@
       <c r="F415" t="n">
         <v>1.65</v>
       </c>
+      <c r="G415" t="n">
+        <v>2.549999999999997</v>
+      </c>
+      <c r="H415" t="n">
+        <v>-2.55</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -10407,6 +12901,12 @@
       <c r="F416" t="n">
         <v>1.77</v>
       </c>
+      <c r="G416" t="n">
+        <v>3.549999999999997</v>
+      </c>
+      <c r="H416" t="n">
+        <v>-3.55</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -10431,6 +12931,12 @@
       <c r="F417" t="n">
         <v>2.03</v>
       </c>
+      <c r="G417" t="n">
+        <v>2.420000000000002</v>
+      </c>
+      <c r="H417" t="n">
+        <v>-2.42</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -10455,6 +12961,12 @@
       <c r="F418" t="n">
         <v>2.43</v>
       </c>
+      <c r="G418" t="n">
+        <v>0.8199999999999932</v>
+      </c>
+      <c r="H418" t="n">
+        <v>-0.8199999999999998</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -10479,6 +12991,12 @@
       <c r="F419" t="n">
         <v>3.82</v>
       </c>
+      <c r="G419" t="n">
+        <v>1.100000000000009</v>
+      </c>
+      <c r="H419" t="n">
+        <v>-1.1</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -10503,6 +13021,12 @@
       <c r="F420" t="n">
         <v>8.27</v>
       </c>
+      <c r="G420" t="n">
+        <v>-1.129999999999995</v>
+      </c>
+      <c r="H420" t="n">
+        <v>1.13</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -10527,6 +13051,12 @@
       <c r="F421" t="n">
         <v>9.09</v>
       </c>
+      <c r="G421" t="n">
+        <v>-9.090000000000003</v>
+      </c>
+      <c r="H421" t="n">
+        <v>9.09</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -10551,6 +13081,12 @@
       <c r="F422" t="n">
         <v>40.74</v>
       </c>
+      <c r="G422" t="n">
+        <v>0.4199999999999946</v>
+      </c>
+      <c r="H422" t="n">
+        <v>-0.4199999999999946</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -10575,6 +13111,12 @@
       <c r="F423" t="n">
         <v>39.19</v>
       </c>
+      <c r="G423" t="n">
+        <v>2.730000000000004</v>
+      </c>
+      <c r="H423" t="n">
+        <v>-2.730000000000004</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -10599,6 +13141,12 @@
       <c r="F424" t="n">
         <v>38.29</v>
       </c>
+      <c r="G424" t="n">
+        <v>4.480000000000004</v>
+      </c>
+      <c r="H424" t="n">
+        <v>-4.480000000000004</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -10623,6 +13171,12 @@
       <c r="F425" t="n">
         <v>39.38</v>
       </c>
+      <c r="G425" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="H425" t="n">
+        <v>-3.32</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -10647,6 +13201,12 @@
       <c r="F426" t="n">
         <v>46.84</v>
       </c>
+      <c r="G426" t="n">
+        <v>-3.940000000000005</v>
+      </c>
+      <c r="H426" t="n">
+        <v>3.940000000000005</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -10671,6 +13231,12 @@
       <c r="F427" t="n">
         <v>43.53</v>
       </c>
+      <c r="G427" t="n">
+        <v>-6.870000000000005</v>
+      </c>
+      <c r="H427" t="n">
+        <v>6.870000000000005</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -10695,6 +13261,12 @@
       <c r="F428" t="n">
         <v>35.79</v>
       </c>
+      <c r="G428" t="n">
+        <v>-3.560000000000002</v>
+      </c>
+      <c r="H428" t="n">
+        <v>3.560000000000002</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -10719,6 +13291,12 @@
       <c r="F429" t="n">
         <v>30.49</v>
       </c>
+      <c r="G429" t="n">
+        <v>0.04000000000000625</v>
+      </c>
+      <c r="H429" t="n">
+        <v>-0.0400000000000027</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -10743,6 +13321,12 @@
       <c r="F430" t="n">
         <v>28.73</v>
       </c>
+      <c r="G430" t="n">
+        <v>1.009999999999991</v>
+      </c>
+      <c r="H430" t="n">
+        <v>-1.009999999999998</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -10767,6 +13351,12 @@
       <c r="F431" t="n">
         <v>27.57</v>
       </c>
+      <c r="G431" t="n">
+        <v>1.27000000000001</v>
+      </c>
+      <c r="H431" t="n">
+        <v>-1.27</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -10791,6 +13381,12 @@
       <c r="F432" t="n">
         <v>27.14</v>
       </c>
+      <c r="G432" t="n">
+        <v>0.6899999999999977</v>
+      </c>
+      <c r="H432" t="n">
+        <v>-0.6899999999999977</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -10815,6 +13411,12 @@
       <c r="F433" t="n">
         <v>25.36</v>
       </c>
+      <c r="G433" t="n">
+        <v>0.5100000000000051</v>
+      </c>
+      <c r="H433" t="n">
+        <v>-0.5100000000000016</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -10839,6 +13441,12 @@
       <c r="F434" t="n">
         <v>16.93</v>
       </c>
+      <c r="G434" t="n">
+        <v>-0.1700000000000017</v>
+      </c>
+      <c r="H434" t="n">
+        <v>0.1699999999999982</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -10863,6 +13471,12 @@
       <c r="F435" t="n">
         <v>5.12</v>
       </c>
+      <c r="G435" t="n">
+        <v>-0.1800000000000068</v>
+      </c>
+      <c r="H435" t="n">
+        <v>0.1799999999999997</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -10887,6 +13501,12 @@
       <c r="F436" t="n">
         <v>1.95</v>
       </c>
+      <c r="G436" t="n">
+        <v>0.3100000000000023</v>
+      </c>
+      <c r="H436" t="n">
+        <v>-0.3099999999999998</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -10911,6 +13531,12 @@
       <c r="F437" t="n">
         <v>1.46</v>
       </c>
+      <c r="G437" t="n">
+        <v>0.5600000000000023</v>
+      </c>
+      <c r="H437" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -10935,6 +13561,12 @@
       <c r="F438" t="n">
         <v>1.39</v>
       </c>
+      <c r="G438" t="n">
+        <v>0.4099999999999966</v>
+      </c>
+      <c r="H438" t="n">
+        <v>-0.4100000000000001</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -10959,6 +13591,12 @@
       <c r="F439" t="n">
         <v>1.33</v>
       </c>
+      <c r="G439" t="n">
+        <v>-0.2800000000000011</v>
+      </c>
+      <c r="H439" t="n">
+        <v>0.28</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -10983,6 +13621,12 @@
       <c r="F440" t="n">
         <v>3.04</v>
       </c>
+      <c r="G440" t="n">
+        <v>-1.060000000000002</v>
+      </c>
+      <c r="H440" t="n">
+        <v>1.06</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -11007,6 +13651,12 @@
       <c r="F441" t="n">
         <v>7.64</v>
       </c>
+      <c r="G441" t="n">
+        <v>-5.930000000000007</v>
+      </c>
+      <c r="H441" t="n">
+        <v>5.93</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -11031,6 +13681,12 @@
       <c r="F442" t="n">
         <v>8.1</v>
       </c>
+      <c r="G442" t="n">
+        <v>-4.179999999999993</v>
+      </c>
+      <c r="H442" t="n">
+        <v>4.18</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -11055,6 +13711,12 @@
       <c r="F443" t="n">
         <v>71.55</v>
       </c>
+      <c r="G443" t="n">
+        <v>-3.470000000000002</v>
+      </c>
+      <c r="H443" t="n">
+        <v>3.469999999999999</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -11079,6 +13741,12 @@
       <c r="F444" t="n">
         <v>66.48999999999999</v>
       </c>
+      <c r="G444" t="n">
+        <v>-4.399999999999999</v>
+      </c>
+      <c r="H444" t="n">
+        <v>4.399999999999991</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -11103,6 +13771,12 @@
       <c r="F445" t="n">
         <v>64.13</v>
       </c>
+      <c r="G445" t="n">
+        <v>-2.450000000000003</v>
+      </c>
+      <c r="H445" t="n">
+        <v>2.449999999999996</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -11127,6 +13801,12 @@
       <c r="F446" t="n">
         <v>66.65000000000001</v>
       </c>
+      <c r="G446" t="n">
+        <v>-5.089999999999996</v>
+      </c>
+      <c r="H446" t="n">
+        <v>5.090000000000003</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -11151,6 +13831,12 @@
       <c r="F447" t="n">
         <v>77.23</v>
       </c>
+      <c r="G447" t="n">
+        <v>-5.550000000000001</v>
+      </c>
+      <c r="H447" t="n">
+        <v>5.549999999999997</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -11175,6 +13861,12 @@
       <c r="F448" t="n">
         <v>73.45</v>
       </c>
+      <c r="G448" t="n">
+        <v>-3.73</v>
+      </c>
+      <c r="H448" t="n">
+        <v>3.730000000000004</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -11199,6 +13891,12 @@
       <c r="F449" t="n">
         <v>62.38</v>
       </c>
+      <c r="G449" t="n">
+        <v>-1.940000000000005</v>
+      </c>
+      <c r="H449" t="n">
+        <v>1.940000000000005</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -11223,6 +13921,12 @@
       <c r="F450" t="n">
         <v>56.2</v>
       </c>
+      <c r="G450" t="n">
+        <v>0.1299999999999955</v>
+      </c>
+      <c r="H450" t="n">
+        <v>-0.1299999999999955</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -11247,6 +13951,12 @@
       <c r="F451" t="n">
         <v>50.73</v>
       </c>
+      <c r="G451" t="n">
+        <v>1.520000000000003</v>
+      </c>
+      <c r="H451" t="n">
+        <v>-1.520000000000003</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -11271,6 +13981,12 @@
       <c r="F452" t="n">
         <v>47.57</v>
       </c>
+      <c r="G452" t="n">
+        <v>-0.5300000000000011</v>
+      </c>
+      <c r="H452" t="n">
+        <v>0.5300000000000011</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -11295,6 +14011,12 @@
       <c r="F453" t="n">
         <v>43.2</v>
       </c>
+      <c r="G453" t="n">
+        <v>0.8900000000000006</v>
+      </c>
+      <c r="H453" t="n">
+        <v>-0.8900000000000006</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -11319,6 +14041,12 @@
       <c r="F454" t="n">
         <v>38.93</v>
       </c>
+      <c r="G454" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H454" t="n">
+        <v>-3.25</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -11343,6 +14071,12 @@
       <c r="F455" t="n">
         <v>30.18</v>
       </c>
+      <c r="G455" t="n">
+        <v>1.929999999999993</v>
+      </c>
+      <c r="H455" t="n">
+        <v>-1.93</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -11367,6 +14101,12 @@
       <c r="F456" t="n">
         <v>10.92</v>
       </c>
+      <c r="G456" t="n">
+        <v>2.099999999999994</v>
+      </c>
+      <c r="H456" t="n">
+        <v>-2.1</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -11391,6 +14131,12 @@
       <c r="F457" t="n">
         <v>4.22</v>
       </c>
+      <c r="G457" t="n">
+        <v>3.420000000000002</v>
+      </c>
+      <c r="H457" t="n">
+        <v>-3.42</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -11415,6 +14161,12 @@
       <c r="F458" t="n">
         <v>3.28</v>
       </c>
+      <c r="G458" t="n">
+        <v>4.329999999999998</v>
+      </c>
+      <c r="H458" t="n">
+        <v>-4.33</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -11439,6 +14191,12 @@
       <c r="F459" t="n">
         <v>2.69</v>
       </c>
+      <c r="G459" t="n">
+        <v>3.740000000000009</v>
+      </c>
+      <c r="H459" t="n">
+        <v>-3.74</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -11463,6 +14221,12 @@
       <c r="F460" t="n">
         <v>2.98</v>
       </c>
+      <c r="G460" t="n">
+        <v>3.789999999999992</v>
+      </c>
+      <c r="H460" t="n">
+        <v>-3.79</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -11487,6 +14251,12 @@
       <c r="F461" t="n">
         <v>4.99</v>
       </c>
+      <c r="G461" t="n">
+        <v>2.050000000000011</v>
+      </c>
+      <c r="H461" t="n">
+        <v>-2.05</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -11511,6 +14281,12 @@
       <c r="F462" t="n">
         <v>10.19</v>
       </c>
+      <c r="G462" t="n">
+        <v>-0.09000000000000341</v>
+      </c>
+      <c r="H462" t="n">
+        <v>0.08999999999999986</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -11535,6 +14311,12 @@
       <c r="F463" t="n">
         <v>9.619999999999999</v>
       </c>
+      <c r="G463" t="n">
+        <v>4.019999999999996</v>
+      </c>
+      <c r="H463" t="n">
+        <v>-4.020000000000001</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -11559,6 +14341,12 @@
       <c r="F464" t="n">
         <v>11.47</v>
       </c>
+      <c r="G464" t="n">
+        <v>3.640000000000001</v>
+      </c>
+      <c r="H464" t="n">
+        <v>-3.639999999999999</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -11583,6 +14371,12 @@
       <c r="F465" t="n">
         <v>9.58</v>
       </c>
+      <c r="G465" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="H465" t="n">
+        <v>-10.66</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -11607,6 +14401,12 @@
       <c r="F466" t="n">
         <v>9.949999999999999</v>
       </c>
+      <c r="G466" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="H466" t="n">
+        <v>-11.14</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -11631,6 +14431,12 @@
       <c r="F467" t="n">
         <v>14.53</v>
       </c>
+      <c r="G467" t="n">
+        <v>8.829999999999998</v>
+      </c>
+      <c r="H467" t="n">
+        <v>-8.83</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -11655,6 +14461,12 @@
       <c r="F468" t="n">
         <v>32.86</v>
       </c>
+      <c r="G468" t="n">
+        <v>-1.469999999999999</v>
+      </c>
+      <c r="H468" t="n">
+        <v>1.469999999999999</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -11679,6 +14491,12 @@
       <c r="F469" t="n">
         <v>27.76</v>
       </c>
+      <c r="G469" t="n">
+        <v>-0.4100000000000108</v>
+      </c>
+      <c r="H469" t="n">
+        <v>0.4100000000000001</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -11703,6 +14521,12 @@
       <c r="F470" t="n">
         <v>19.54</v>
       </c>
+      <c r="G470" t="n">
+        <v>2.36999999999999</v>
+      </c>
+      <c r="H470" t="n">
+        <v>-2.370000000000001</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -11727,6 +14551,12 @@
       <c r="F471" t="n">
         <v>15.58</v>
       </c>
+      <c r="G471" t="n">
+        <v>2.960000000000008</v>
+      </c>
+      <c r="H471" t="n">
+        <v>-2.959999999999999</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -11751,6 +14581,12 @@
       <c r="F472" t="n">
         <v>14.52</v>
       </c>
+      <c r="G472" t="n">
+        <v>5.670000000000002</v>
+      </c>
+      <c r="H472" t="n">
+        <v>-5.670000000000002</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -11775,6 +14611,12 @@
       <c r="F473" t="n">
         <v>14.14</v>
       </c>
+      <c r="G473" t="n">
+        <v>4.030000000000001</v>
+      </c>
+      <c r="H473" t="n">
+        <v>-4.030000000000001</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -11799,6 +14641,12 @@
       <c r="F474" t="n">
         <v>12.49</v>
       </c>
+      <c r="G474" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="H474" t="n">
+        <v>-9.889999999999999</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -11823,6 +14671,12 @@
       <c r="F475" t="n">
         <v>11.77</v>
       </c>
+      <c r="G475" t="n">
+        <v>6.049999999999997</v>
+      </c>
+      <c r="H475" t="n">
+        <v>-6.050000000000001</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -11847,6 +14701,12 @@
       <c r="F476" t="n">
         <v>9.5</v>
       </c>
+      <c r="G476" t="n">
+        <v>6.670000000000002</v>
+      </c>
+      <c r="H476" t="n">
+        <v>-6.670000000000002</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -11871,6 +14731,12 @@
       <c r="F477" t="n">
         <v>4.12</v>
       </c>
+      <c r="G477" t="n">
+        <v>9.539999999999992</v>
+      </c>
+      <c r="H477" t="n">
+        <v>-9.539999999999999</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -11895,6 +14761,12 @@
       <c r="F478" t="n">
         <v>1.02</v>
       </c>
+      <c r="G478" t="n">
+        <v>7.340000000000003</v>
+      </c>
+      <c r="H478" t="n">
+        <v>-7.34</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -11919,6 +14791,12 @@
       <c r="F479" t="n">
         <v>1.11</v>
       </c>
+      <c r="G479" t="n">
+        <v>1.019999999999996</v>
+      </c>
+      <c r="H479" t="n">
+        <v>-1.02</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -11943,6 +14821,12 @@
       <c r="F480" t="n">
         <v>3.15</v>
       </c>
+      <c r="G480" t="n">
+        <v>0.9699999999999989</v>
+      </c>
+      <c r="H480" t="n">
+        <v>-0.9700000000000002</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -11967,6 +14851,12 @@
       <c r="F481" t="n">
         <v>3.07</v>
       </c>
+      <c r="G481" t="n">
+        <v>0.6200000000000045</v>
+      </c>
+      <c r="H481" t="n">
+        <v>-0.6200000000000001</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -11991,6 +14881,12 @@
       <c r="F482" t="n">
         <v>2.95</v>
       </c>
+      <c r="G482" t="n">
+        <v>6.009999999999991</v>
+      </c>
+      <c r="H482" t="n">
+        <v>-6.010000000000001</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -12015,6 +14911,12 @@
       <c r="F483" t="n">
         <v>8.699999999999999</v>
       </c>
+      <c r="G483" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="H483" t="n">
+        <v>-41.3</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -12039,6 +14941,12 @@
       <c r="F484" t="n">
         <v>0</v>
       </c>
+      <c r="G484" t="n">
+        <v>0</v>
+      </c>
+      <c r="H484" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -12063,6 +14971,12 @@
       <c r="F485" t="n">
         <v>47.37</v>
       </c>
+      <c r="G485" t="n">
+        <v>-2.909999999999997</v>
+      </c>
+      <c r="H485" t="n">
+        <v>2.909999999999997</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -12087,6 +15001,12 @@
       <c r="F486" t="n">
         <v>41.28</v>
       </c>
+      <c r="G486" t="n">
+        <v>1.560000000000002</v>
+      </c>
+      <c r="H486" t="n">
+        <v>-1.560000000000002</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -12111,6 +15031,12 @@
       <c r="F487" t="n">
         <v>36.26</v>
       </c>
+      <c r="G487" t="n">
+        <v>5.940000000000005</v>
+      </c>
+      <c r="H487" t="n">
+        <v>-5.940000000000005</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -12135,6 +15061,12 @@
       <c r="F488" t="n">
         <v>36.74</v>
       </c>
+      <c r="G488" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="H488" t="n">
+        <v>-4.18</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -12159,6 +15091,12 @@
       <c r="F489" t="n">
         <v>48.71</v>
       </c>
+      <c r="G489" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H489" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -12183,6 +15121,12 @@
       <c r="F490" t="n">
         <v>48.26</v>
       </c>
+      <c r="G490" t="n">
+        <v>-3.809999999999995</v>
+      </c>
+      <c r="H490" t="n">
+        <v>3.809999999999995</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -12207,6 +15151,12 @@
       <c r="F491" t="n">
         <v>42.31</v>
       </c>
+      <c r="G491" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="H491" t="n">
+        <v>2.43</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -12231,6 +15181,12 @@
       <c r="F492" t="n">
         <v>35.84</v>
       </c>
+      <c r="G492" t="n">
+        <v>0.8199999999999932</v>
+      </c>
+      <c r="H492" t="n">
+        <v>-0.8199999999999932</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -12255,6 +15211,12 @@
       <c r="F493" t="n">
         <v>31.94</v>
       </c>
+      <c r="G493" t="n">
+        <v>2.079999999999998</v>
+      </c>
+      <c r="H493" t="n">
+        <v>-2.080000000000002</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -12279,6 +15241,12 @@
       <c r="F494" t="n">
         <v>30.67</v>
       </c>
+      <c r="G494" t="n">
+        <v>0.9500000000000028</v>
+      </c>
+      <c r="H494" t="n">
+        <v>-0.9499999999999993</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -12303,6 +15271,12 @@
       <c r="F495" t="n">
         <v>29.12</v>
       </c>
+      <c r="G495" t="n">
+        <v>0.8999999999999915</v>
+      </c>
+      <c r="H495" t="n">
+        <v>-0.8999999999999986</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -12327,6 +15301,12 @@
       <c r="F496" t="n">
         <v>26.19</v>
       </c>
+      <c r="G496" t="n">
+        <v>2.430000000000007</v>
+      </c>
+      <c r="H496" t="n">
+        <v>-2.43</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -12351,6 +15331,12 @@
       <c r="F497" t="n">
         <v>19.27</v>
       </c>
+      <c r="G497" t="n">
+        <v>2.52000000000001</v>
+      </c>
+      <c r="H497" t="n">
+        <v>-2.52</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -12375,6 +15361,12 @@
       <c r="F498" t="n">
         <v>7.14</v>
       </c>
+      <c r="G498" t="n">
+        <v>0.8900000000000006</v>
+      </c>
+      <c r="H498" t="n">
+        <v>-0.8899999999999997</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -12399,6 +15391,12 @@
       <c r="F499" t="n">
         <v>3.16</v>
       </c>
+      <c r="G499" t="n">
+        <v>1.409999999999997</v>
+      </c>
+      <c r="H499" t="n">
+        <v>-1.41</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -12423,6 +15421,12 @@
       <c r="F500" t="n">
         <v>2.65</v>
       </c>
+      <c r="G500" t="n">
+        <v>2.709999999999994</v>
+      </c>
+      <c r="H500" t="n">
+        <v>-2.71</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -12447,6 +15451,12 @@
       <c r="F501" t="n">
         <v>2.38</v>
       </c>
+      <c r="G501" t="n">
+        <v>1.800000000000011</v>
+      </c>
+      <c r="H501" t="n">
+        <v>-1.8</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -12471,6 +15481,12 @@
       <c r="F502" t="n">
         <v>2.3</v>
       </c>
+      <c r="G502" t="n">
+        <v>1.620000000000005</v>
+      </c>
+      <c r="H502" t="n">
+        <v>-1.62</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -12495,6 +15511,12 @@
       <c r="F503" t="n">
         <v>4.96</v>
       </c>
+      <c r="G503" t="n">
+        <v>-1.069999999999993</v>
+      </c>
+      <c r="H503" t="n">
+        <v>1.07</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -12519,6 +15541,12 @@
       <c r="F504" t="n">
         <v>9.960000000000001</v>
       </c>
+      <c r="G504" t="n">
+        <v>-5.759999999999991</v>
+      </c>
+      <c r="H504" t="n">
+        <v>5.760000000000001</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -12542,6 +15570,12 @@
       </c>
       <c r="F505" t="n">
         <v>12.88</v>
+      </c>
+      <c r="G505" t="n">
+        <v>-6.429999999999993</v>
+      </c>
+      <c r="H505" t="n">
+        <v>6.430000000000001</v>
       </c>
     </row>
   </sheetData>
